--- a/wwwroot/template/TmSendMailNew.xlsx
+++ b/wwwroot/template/TmSendMailNew.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\khanhmf\Cost Managerment\wwwroot\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3474312C-F61A-4AB6-88A7-6BF681079FD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F34111EF-9665-459B-937B-7FF9F4C4541B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{2DA54543-7852-4C3B-B81A-134334FCB771}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{2DA54543-7852-4C3B-B81A-134334FCB771}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -95,7 +95,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="154">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="155">
   <si>
     <t>Company name</t>
   </si>
@@ -579,6 +579,9 @@
   </si>
   <si>
     <t>Pallet</t>
+  </si>
+  <si>
+    <t>Quantity(*)</t>
   </si>
 </sst>
 </file>
@@ -836,6 +839,17 @@
     <xf numFmtId="165" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="15" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -856,17 +870,6 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="15" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1348,32 +1351,32 @@
       <c r="AM3" s="1"/>
     </row>
     <row r="4" spans="1:41" s="5" customFormat="1" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A4" s="22" t="s">
+      <c r="A4" s="27" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="22"/>
-      <c r="C4" s="22"/>
-      <c r="D4" s="22"/>
-      <c r="E4" s="22"/>
-      <c r="F4" s="22"/>
-      <c r="G4" s="22"/>
-      <c r="H4" s="22"/>
-      <c r="I4" s="22"/>
-      <c r="J4" s="22"/>
-      <c r="K4" s="22"/>
-      <c r="L4" s="22"/>
-      <c r="M4" s="22"/>
-      <c r="N4" s="22"/>
-      <c r="O4" s="22"/>
-      <c r="P4" s="22"/>
-      <c r="Q4" s="22"/>
-      <c r="R4" s="22"/>
-      <c r="S4" s="22"/>
-      <c r="T4" s="22"/>
-      <c r="U4" s="22"/>
-      <c r="V4" s="22"/>
-      <c r="W4" s="22"/>
-      <c r="X4" s="22"/>
+      <c r="B4" s="27"/>
+      <c r="C4" s="27"/>
+      <c r="D4" s="27"/>
+      <c r="E4" s="27"/>
+      <c r="F4" s="27"/>
+      <c r="G4" s="27"/>
+      <c r="H4" s="27"/>
+      <c r="I4" s="27"/>
+      <c r="J4" s="27"/>
+      <c r="K4" s="27"/>
+      <c r="L4" s="27"/>
+      <c r="M4" s="27"/>
+      <c r="N4" s="27"/>
+      <c r="O4" s="27"/>
+      <c r="P4" s="27"/>
+      <c r="Q4" s="27"/>
+      <c r="R4" s="27"/>
+      <c r="S4" s="27"/>
+      <c r="T4" s="27"/>
+      <c r="U4" s="27"/>
+      <c r="V4" s="27"/>
+      <c r="W4" s="27"/>
+      <c r="X4" s="27"/>
       <c r="Y4" s="1"/>
       <c r="Z4" s="1"/>
       <c r="AA4" s="1"/>
@@ -1569,32 +1572,32 @@
       <c r="AM8" s="1"/>
     </row>
     <row r="9" spans="1:41" s="5" customFormat="1" ht="66" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="23" t="s">
+      <c r="A9" s="28" t="s">
         <v>12</v>
       </c>
-      <c r="B9" s="23"/>
-      <c r="C9" s="23"/>
-      <c r="D9" s="23"/>
-      <c r="E9" s="23"/>
-      <c r="F9" s="23"/>
-      <c r="G9" s="23"/>
-      <c r="H9" s="23"/>
-      <c r="I9" s="23"/>
-      <c r="J9" s="23"/>
-      <c r="K9" s="23"/>
-      <c r="L9" s="23"/>
-      <c r="M9" s="23"/>
-      <c r="N9" s="23"/>
-      <c r="O9" s="23"/>
-      <c r="P9" s="23"/>
-      <c r="Q9" s="23"/>
-      <c r="R9" s="23"/>
-      <c r="S9" s="23"/>
-      <c r="T9" s="23"/>
-      <c r="U9" s="23"/>
-      <c r="V9" s="23"/>
-      <c r="W9" s="23"/>
-      <c r="X9" s="23"/>
+      <c r="B9" s="28"/>
+      <c r="C9" s="28"/>
+      <c r="D9" s="28"/>
+      <c r="E9" s="28"/>
+      <c r="F9" s="28"/>
+      <c r="G9" s="28"/>
+      <c r="H9" s="28"/>
+      <c r="I9" s="28"/>
+      <c r="J9" s="28"/>
+      <c r="K9" s="28"/>
+      <c r="L9" s="28"/>
+      <c r="M9" s="28"/>
+      <c r="N9" s="28"/>
+      <c r="O9" s="28"/>
+      <c r="P9" s="28"/>
+      <c r="Q9" s="28"/>
+      <c r="R9" s="28"/>
+      <c r="S9" s="28"/>
+      <c r="T9" s="28"/>
+      <c r="U9" s="28"/>
+      <c r="V9" s="28"/>
+      <c r="W9" s="28"/>
+      <c r="X9" s="28"/>
       <c r="Y9" s="10"/>
       <c r="Z9" s="10"/>
       <c r="AA9" s="10"/>
@@ -1614,41 +1617,41 @@
       <c r="AO9" s="10"/>
     </row>
     <row r="10" spans="1:41" ht="73.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="24" t="s">
+      <c r="A10" s="29" t="s">
         <v>13</v>
       </c>
-      <c r="B10" s="24"/>
-      <c r="C10" s="24"/>
-      <c r="D10" s="24"/>
-      <c r="E10" s="24"/>
-      <c r="F10" s="24"/>
-      <c r="G10" s="24"/>
-      <c r="H10" s="24"/>
-      <c r="I10" s="24"/>
-      <c r="J10" s="24"/>
-      <c r="K10" s="25" t="s">
+      <c r="B10" s="29"/>
+      <c r="C10" s="29"/>
+      <c r="D10" s="29"/>
+      <c r="E10" s="29"/>
+      <c r="F10" s="29"/>
+      <c r="G10" s="29"/>
+      <c r="H10" s="29"/>
+      <c r="I10" s="29"/>
+      <c r="J10" s="29"/>
+      <c r="K10" s="30" t="s">
         <v>14</v>
       </c>
-      <c r="L10" s="26"/>
-      <c r="M10" s="26"/>
-      <c r="N10" s="26"/>
-      <c r="O10" s="26"/>
-      <c r="P10" s="26"/>
-      <c r="Q10" s="26"/>
-      <c r="R10" s="26"/>
-      <c r="S10" s="26"/>
-      <c r="T10" s="26"/>
-      <c r="U10" s="26"/>
-      <c r="V10" s="26"/>
-      <c r="W10" s="26"/>
-      <c r="X10" s="26"/>
-      <c r="Y10" s="27" t="s">
+      <c r="L10" s="31"/>
+      <c r="M10" s="31"/>
+      <c r="N10" s="31"/>
+      <c r="O10" s="31"/>
+      <c r="P10" s="31"/>
+      <c r="Q10" s="31"/>
+      <c r="R10" s="31"/>
+      <c r="S10" s="31"/>
+      <c r="T10" s="31"/>
+      <c r="U10" s="31"/>
+      <c r="V10" s="31"/>
+      <c r="W10" s="31"/>
+      <c r="X10" s="31"/>
+      <c r="Y10" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="Z10" s="28"/>
-      <c r="AA10" s="28"/>
-      <c r="AB10" s="28"/>
-      <c r="AC10" s="28"/>
+      <c r="Z10" s="33"/>
+      <c r="AA10" s="33"/>
+      <c r="AB10" s="33"/>
+      <c r="AC10" s="33"/>
     </row>
     <row r="11" spans="1:41" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="11">
@@ -1780,7 +1783,7 @@
         <v>27</v>
       </c>
       <c r="N12" s="14" t="s">
-        <v>21</v>
+        <v>154</v>
       </c>
       <c r="O12" s="14" t="s">
         <v>22</v>
@@ -3897,562 +3900,562 @@
       </c>
     </row>
     <row r="2" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B2" s="29" t="s">
+      <c r="B2" s="22" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="3" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B3" s="30" t="s">
+      <c r="B3" s="23" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="4" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B4" s="30" t="s">
+      <c r="B4" s="23" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="5" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B5" s="30" t="s">
+      <c r="B5" s="23" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="6" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B6" s="30" t="s">
+      <c r="B6" s="23" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="7" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B7" s="30" t="s">
+      <c r="B7" s="23" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="8" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B8" s="30" t="s">
+      <c r="B8" s="23" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="9" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B9" s="31" t="s">
+      <c r="B9" s="24" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="10" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B10" s="31" t="s">
+      <c r="B10" s="24" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="11" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B11" s="30" t="s">
+      <c r="B11" s="23" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="12" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B12" s="31" t="s">
+      <c r="B12" s="24" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="13" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B13" s="30" t="s">
+      <c r="B13" s="23" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="14" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B14" s="30" t="s">
+      <c r="B14" s="23" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="15" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B15" s="30" t="s">
+      <c r="B15" s="23" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="16" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B16" s="30" t="s">
+      <c r="B16" s="23" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="17" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B17" s="30" t="s">
+      <c r="B17" s="23" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="18" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B18" s="30" t="s">
+      <c r="B18" s="23" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="19" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B19" s="30" t="s">
+      <c r="B19" s="23" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="20" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B20" s="31" t="s">
+      <c r="B20" s="24" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="21" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B21" s="31" t="s">
+      <c r="B21" s="24" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="22" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B22" s="31" t="s">
+      <c r="B22" s="24" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="23" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B23" s="30" t="s">
+      <c r="B23" s="23" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="24" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B24" s="31" t="s">
+      <c r="B24" s="24" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="25" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B25" s="30" t="s">
+      <c r="B25" s="23" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="26" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B26" s="31" t="s">
+      <c r="B26" s="24" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="27" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B27" s="31" t="s">
+      <c r="B27" s="24" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="28" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B28" s="30" t="s">
+      <c r="B28" s="23" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="29" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B29" s="30" t="s">
+      <c r="B29" s="23" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="30" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B30" s="31" t="s">
+      <c r="B30" s="24" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="31" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B31" s="31" t="s">
+      <c r="B31" s="24" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="32" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B32" s="30" t="s">
+      <c r="B32" s="23" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="33" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B33" s="30" t="s">
+      <c r="B33" s="23" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="34" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B34" s="30" t="s">
+      <c r="B34" s="23" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="35" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B35" s="30" t="s">
+      <c r="B35" s="23" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="36" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B36" s="30" t="s">
+      <c r="B36" s="23" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="37" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B37" s="30" t="s">
+      <c r="B37" s="23" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="38" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B38" s="30" t="s">
+      <c r="B38" s="23" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="39" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B39" s="31" t="s">
+      <c r="B39" s="24" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="40" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B40" s="30" t="s">
+      <c r="B40" s="23" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="41" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B41" s="30" t="s">
+      <c r="B41" s="23" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="42" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B42" s="30" t="s">
+      <c r="B42" s="23" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="43" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B43" s="30" t="s">
+      <c r="B43" s="23" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="44" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B44" s="30" t="s">
+      <c r="B44" s="23" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="45" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B45" s="30" t="s">
+      <c r="B45" s="23" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="46" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B46" s="30" t="s">
+      <c r="B46" s="23" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="47" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B47" s="30" t="s">
+      <c r="B47" s="23" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="48" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B48" s="30" t="s">
+      <c r="B48" s="23" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="49" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B49" s="30" t="s">
+      <c r="B49" s="23" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="50" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B50" s="30" t="s">
+      <c r="B50" s="23" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="51" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B51" s="30" t="s">
+      <c r="B51" s="23" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="52" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B52" s="30" t="s">
+      <c r="B52" s="23" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="53" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B53" s="30" t="s">
+      <c r="B53" s="23" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="54" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B54" s="30" t="s">
+      <c r="B54" s="23" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="55" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B55" s="31" t="s">
+      <c r="B55" s="24" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="56" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B56" s="31" t="s">
+      <c r="B56" s="24" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="57" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B57" s="31" t="s">
+      <c r="B57" s="24" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="58" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B58" s="30" t="s">
+      <c r="B58" s="23" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="59" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B59" s="30" t="s">
+      <c r="B59" s="23" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="60" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B60" s="31" t="s">
+      <c r="B60" s="24" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="61" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B61" s="30" t="s">
+      <c r="B61" s="23" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="62" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B62" s="30" t="s">
+      <c r="B62" s="23" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="63" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B63" s="30" t="s">
+      <c r="B63" s="23" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="64" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B64" s="30" t="s">
+      <c r="B64" s="23" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="65" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B65" s="30" t="s">
+      <c r="B65" s="23" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="66" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B66" s="30" t="s">
+      <c r="B66" s="23" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="67" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B67" s="30" t="s">
+      <c r="B67" s="23" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="68" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B68" s="31" t="s">
+      <c r="B68" s="24" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="69" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B69" s="31" t="s">
+      <c r="B69" s="24" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="70" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B70" s="30" t="s">
+      <c r="B70" s="23" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="71" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B71" s="31" t="s">
+      <c r="B71" s="24" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="72" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B72" s="30" t="s">
+      <c r="B72" s="23" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="73" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B73" s="30" t="s">
+      <c r="B73" s="23" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="74" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B74" s="30" t="s">
+      <c r="B74" s="23" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="75" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B75" s="30" t="s">
+      <c r="B75" s="23" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="76" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B76" s="30" t="s">
+      <c r="B76" s="23" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="77" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B77" s="30" t="s">
+      <c r="B77" s="23" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="78" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B78" s="30" t="s">
+      <c r="B78" s="23" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="79" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B79" s="30" t="s">
+      <c r="B79" s="23" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="80" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B80" s="30" t="s">
+      <c r="B80" s="23" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="81" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B81" s="30" t="s">
+      <c r="B81" s="23" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="82" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B82" s="30" t="s">
+      <c r="B82" s="23" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="83" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B83" s="31" t="s">
+      <c r="B83" s="24" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="84" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B84" s="30" t="s">
+      <c r="B84" s="23" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="85" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B85" s="30" t="s">
+      <c r="B85" s="23" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="86" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B86" s="30" t="s">
+      <c r="B86" s="23" t="s">
         <v>126</v>
       </c>
     </row>
     <row r="87" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="31" t="s">
+      <c r="B87" s="24" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="88" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B88" s="30" t="s">
+      <c r="B88" s="23" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="89" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B89" s="30" t="s">
+      <c r="B89" s="23" t="s">
         <v>129</v>
       </c>
     </row>
     <row r="90" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B90" s="30" t="s">
+      <c r="B90" s="23" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="91" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B91" s="30" t="s">
+      <c r="B91" s="23" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="92" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B92" s="30" t="s">
+      <c r="B92" s="23" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="93" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B93" s="30" t="s">
+      <c r="B93" s="23" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="94" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B94" s="30" t="s">
+      <c r="B94" s="23" t="s">
         <v>134</v>
       </c>
     </row>
     <row r="95" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B95" s="30" t="s">
+      <c r="B95" s="23" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="96" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B96" s="30" t="s">
+      <c r="B96" s="23" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="97" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B97" s="31" t="s">
+      <c r="B97" s="24" t="s">
         <v>137</v>
       </c>
     </row>
     <row r="98" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B98" s="30" t="s">
+      <c r="B98" s="23" t="s">
         <v>138</v>
       </c>
     </row>
     <row r="99" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B99" s="30" t="s">
+      <c r="B99" s="23" t="s">
         <v>139</v>
       </c>
     </row>
     <row r="100" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B100" s="30" t="s">
+      <c r="B100" s="23" t="s">
         <v>140</v>
       </c>
     </row>
     <row r="101" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B101" s="30" t="s">
+      <c r="B101" s="23" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="102" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B102" s="30" t="s">
+      <c r="B102" s="23" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="103" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B103" s="30" t="s">
+      <c r="B103" s="23" t="s">
         <v>143</v>
       </c>
     </row>
     <row r="104" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B104" s="30" t="s">
+      <c r="B104" s="23" t="s">
         <v>144</v>
       </c>
     </row>
     <row r="105" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B105" s="30" t="s">
+      <c r="B105" s="23" t="s">
         <v>145</v>
       </c>
     </row>
     <row r="106" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B106" s="31" t="s">
+      <c r="B106" s="24" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="107" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B107" s="31" t="s">
+      <c r="B107" s="24" t="s">
         <v>147</v>
       </c>
     </row>
     <row r="108" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B108" s="30" t="s">
+      <c r="B108" s="23" t="s">
         <v>148</v>
       </c>
     </row>
     <row r="109" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B109" s="32" t="s">
+      <c r="B109" s="25" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="110" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B110" s="33" t="s">
+      <c r="B110" s="26" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="111" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B111" s="32" t="s">
+      <c r="B111" s="25" t="s">
         <v>151</v>
       </c>
     </row>
     <row r="112" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B112" s="32" t="s">
+      <c r="B112" s="25" t="s">
         <v>152</v>
       </c>
     </row>
     <row r="113" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B113" s="30" t="s">
+      <c r="B113" s="23" t="s">
         <v>153</v>
       </c>
     </row>

--- a/wwwroot/template/TmSendMailNew.xlsx
+++ b/wwwroot/template/TmSendMailNew.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\khanhmf\Cost Managerment\wwwroot\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F34111EF-9665-459B-937B-7FF9F4C4541B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73B94A57-874D-4FFF-93BD-5D4A623E828D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{2DA54543-7852-4C3B-B81A-134334FCB771}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{2DA54543-7852-4C3B-B81A-134334FCB771}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -95,7 +95,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="158">
   <si>
     <t>Company name</t>
   </si>
@@ -582,6 +582,15 @@
   </si>
   <si>
     <t>Quantity(*)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ID request</t>
+  </si>
+  <si>
+    <t>Price effective date</t>
+  </si>
+  <si>
+    <t>Expiration date of the price</t>
   </si>
 </sst>
 </file>
@@ -1207,17 +1216,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{612B90E7-BC5D-4BEC-8F3F-8E9549A9E0DD}">
-  <dimension ref="A1:AO77"/>
+  <dimension ref="A1:AR77"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="12.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="15" width="8.7109375" style="1"/>
     <col min="16" max="16" width="11.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="17" max="21" width="8.7109375" style="1"/>
     <col min="22" max="22" width="17.42578125" style="1" customWidth="1"/>
-    <col min="23" max="16384" width="8.7109375" style="1"/>
+    <col min="23" max="25" width="8.7109375" style="1"/>
+    <col min="26" max="26" width="10" style="1" customWidth="1"/>
+    <col min="27" max="29" width="8.7109375" style="1"/>
+    <col min="30" max="30" width="9.7109375" style="1" customWidth="1"/>
+    <col min="31" max="16384" width="8.7109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:41" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:44" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1261,8 +1274,11 @@
       <c r="AK1" s="1"/>
       <c r="AL1" s="1"/>
       <c r="AM1" s="1"/>
-    </row>
-    <row r="2" spans="1:41" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="AN1" s="1"/>
+      <c r="AO1" s="1"/>
+      <c r="AP1" s="1"/>
+    </row>
+    <row r="2" spans="1:44" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -1306,8 +1322,11 @@
       <c r="AK2" s="1"/>
       <c r="AL2" s="1"/>
       <c r="AM2" s="1"/>
-    </row>
-    <row r="3" spans="1:41" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="AN2" s="1"/>
+      <c r="AO2" s="1"/>
+      <c r="AP2" s="1"/>
+    </row>
+    <row r="3" spans="1:44" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
@@ -1349,8 +1368,11 @@
       <c r="AK3" s="1"/>
       <c r="AL3" s="1"/>
       <c r="AM3" s="1"/>
-    </row>
-    <row r="4" spans="1:41" s="5" customFormat="1" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="AN3" s="1"/>
+      <c r="AO3" s="1"/>
+      <c r="AP3" s="1"/>
+    </row>
+    <row r="4" spans="1:44" s="5" customFormat="1" ht="18.75" x14ac:dyDescent="0.2">
       <c r="A4" s="27" t="s">
         <v>4</v>
       </c>
@@ -1377,8 +1399,8 @@
       <c r="V4" s="27"/>
       <c r="W4" s="27"/>
       <c r="X4" s="27"/>
-      <c r="Y4" s="1"/>
-      <c r="Z4" s="1"/>
+      <c r="Y4" s="27"/>
+      <c r="Z4" s="27"/>
       <c r="AA4" s="1"/>
       <c r="AB4" s="1"/>
       <c r="AC4" s="1"/>
@@ -1392,8 +1414,11 @@
       <c r="AK4" s="1"/>
       <c r="AL4" s="1"/>
       <c r="AM4" s="1"/>
-    </row>
-    <row r="5" spans="1:41" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="AN4" s="1"/>
+      <c r="AO4" s="1"/>
+      <c r="AP4" s="1"/>
+    </row>
+    <row r="5" spans="1:44" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
@@ -1439,8 +1464,11 @@
       <c r="AK5" s="1"/>
       <c r="AL5" s="1"/>
       <c r="AM5" s="1"/>
-    </row>
-    <row r="6" spans="1:41" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="AN5" s="1"/>
+      <c r="AO5" s="1"/>
+      <c r="AP5" s="1"/>
+    </row>
+    <row r="6" spans="1:44" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A6" s="1"/>
       <c r="B6" s="1" t="s">
         <v>8</v>
@@ -1484,8 +1512,11 @@
       <c r="AK6" s="1"/>
       <c r="AL6" s="1"/>
       <c r="AM6" s="1"/>
-    </row>
-    <row r="7" spans="1:41" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="AN6" s="1"/>
+      <c r="AO6" s="1"/>
+      <c r="AP6" s="1"/>
+    </row>
+    <row r="7" spans="1:44" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A7" s="1"/>
       <c r="B7" s="1" t="s">
         <v>10</v>
@@ -1529,8 +1560,11 @@
       <c r="AK7" s="1"/>
       <c r="AL7" s="1"/>
       <c r="AM7" s="1"/>
-    </row>
-    <row r="8" spans="1:41" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="AN7" s="1"/>
+      <c r="AO7" s="1"/>
+      <c r="AP7" s="1"/>
+    </row>
+    <row r="8" spans="1:44" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
@@ -1570,8 +1604,11 @@
       <c r="AK8" s="1"/>
       <c r="AL8" s="1"/>
       <c r="AM8" s="1"/>
-    </row>
-    <row r="9" spans="1:41" s="5" customFormat="1" ht="66" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AN8" s="1"/>
+      <c r="AO8" s="1"/>
+      <c r="AP8" s="1"/>
+    </row>
+    <row r="9" spans="1:44" s="5" customFormat="1" ht="66" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="28" t="s">
         <v>12</v>
       </c>
@@ -1598,8 +1635,8 @@
       <c r="V9" s="28"/>
       <c r="W9" s="28"/>
       <c r="X9" s="28"/>
-      <c r="Y9" s="10"/>
-      <c r="Z9" s="10"/>
+      <c r="Y9" s="28"/>
+      <c r="Z9" s="28"/>
       <c r="AA9" s="10"/>
       <c r="AB9" s="10"/>
       <c r="AC9" s="10"/>
@@ -1615,8 +1652,11 @@
       <c r="AM9" s="10"/>
       <c r="AN9" s="10"/>
       <c r="AO9" s="10"/>
-    </row>
-    <row r="10" spans="1:41" ht="73.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AP9" s="10"/>
+      <c r="AQ9" s="10"/>
+      <c r="AR9" s="10"/>
+    </row>
+    <row r="10" spans="1:44" ht="73.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="29" t="s">
         <v>13</v>
       </c>
@@ -1645,15 +1685,18 @@
       <c r="V10" s="31"/>
       <c r="W10" s="31"/>
       <c r="X10" s="31"/>
-      <c r="Y10" s="32" t="s">
+      <c r="Y10" s="31"/>
+      <c r="Z10" s="31"/>
+      <c r="AA10" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="Z10" s="33"/>
-      <c r="AA10" s="33"/>
       <c r="AB10" s="33"/>
       <c r="AC10" s="33"/>
-    </row>
-    <row r="11" spans="1:41" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AD10" s="33"/>
+      <c r="AE10" s="33"/>
+      <c r="AF10" s="33"/>
+    </row>
+    <row r="11" spans="1:44" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="11">
         <v>1</v>
       </c>
@@ -1741,8 +1784,17 @@
       <c r="AC11" s="11">
         <v>29</v>
       </c>
-    </row>
-    <row r="12" spans="1:41" ht="76.5" x14ac:dyDescent="0.25">
+      <c r="AD11" s="11">
+        <v>30</v>
+      </c>
+      <c r="AE11" s="11">
+        <v>31</v>
+      </c>
+      <c r="AF11" s="11">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="12" spans="1:44" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
         <v>16</v>
       </c>
@@ -1815,23 +1867,32 @@
       <c r="X12" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="Y12" s="13" t="s">
+      <c r="Y12" s="14" t="s">
+        <v>156</v>
+      </c>
+      <c r="Z12" s="14" t="s">
+        <v>157</v>
+      </c>
+      <c r="AA12" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="Z12" s="13" t="s">
+      <c r="AB12" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="AA12" s="13" t="s">
+      <c r="AC12" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="AB12" s="13" t="s">
+      <c r="AD12" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="AC12" s="13" t="s">
+      <c r="AE12" s="13" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="13" spans="1:41" x14ac:dyDescent="0.25">
+      <c r="AF12" s="13" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="13" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A13" s="17"/>
       <c r="B13" s="17"/>
       <c r="C13" s="17"/>
@@ -1856,13 +1917,16 @@
       <c r="V13" s="19"/>
       <c r="W13" s="19"/>
       <c r="X13" s="19"/>
-      <c r="Y13" s="17"/>
-      <c r="Z13" s="17"/>
+      <c r="Y13" s="19"/>
+      <c r="Z13" s="19"/>
       <c r="AA13" s="17"/>
       <c r="AB13" s="17"/>
-      <c r="AC13" s="18"/>
-    </row>
-    <row r="14" spans="1:41" x14ac:dyDescent="0.25">
+      <c r="AC13" s="17"/>
+      <c r="AD13" s="17"/>
+      <c r="AE13" s="17"/>
+      <c r="AF13" s="18"/>
+    </row>
+    <row r="14" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A14" s="17"/>
       <c r="B14" s="17"/>
       <c r="C14" s="17"/>
@@ -1887,13 +1951,16 @@
       <c r="V14" s="19"/>
       <c r="W14" s="19"/>
       <c r="X14" s="19"/>
-      <c r="Y14" s="17"/>
-      <c r="Z14" s="17"/>
+      <c r="Y14" s="19"/>
+      <c r="Z14" s="19"/>
       <c r="AA14" s="17"/>
       <c r="AB14" s="17"/>
-      <c r="AC14" s="18"/>
-    </row>
-    <row r="15" spans="1:41" x14ac:dyDescent="0.25">
+      <c r="AC14" s="17"/>
+      <c r="AD14" s="17"/>
+      <c r="AE14" s="17"/>
+      <c r="AF14" s="18"/>
+    </row>
+    <row r="15" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A15" s="17"/>
       <c r="B15" s="17"/>
       <c r="C15" s="17"/>
@@ -1918,13 +1985,16 @@
       <c r="V15" s="19"/>
       <c r="W15" s="19"/>
       <c r="X15" s="19"/>
-      <c r="Y15" s="17"/>
-      <c r="Z15" s="17"/>
+      <c r="Y15" s="19"/>
+      <c r="Z15" s="19"/>
       <c r="AA15" s="17"/>
       <c r="AB15" s="17"/>
-      <c r="AC15" s="18"/>
-    </row>
-    <row r="16" spans="1:41" x14ac:dyDescent="0.25">
+      <c r="AC15" s="17"/>
+      <c r="AD15" s="17"/>
+      <c r="AE15" s="17"/>
+      <c r="AF15" s="18"/>
+    </row>
+    <row r="16" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A16" s="17"/>
       <c r="B16" s="17"/>
       <c r="C16" s="17"/>
@@ -1949,13 +2019,16 @@
       <c r="V16" s="19"/>
       <c r="W16" s="19"/>
       <c r="X16" s="19"/>
-      <c r="Y16" s="17"/>
-      <c r="Z16" s="17"/>
+      <c r="Y16" s="19"/>
+      <c r="Z16" s="19"/>
       <c r="AA16" s="17"/>
       <c r="AB16" s="17"/>
-      <c r="AC16" s="18"/>
-    </row>
-    <row r="17" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AC16" s="17"/>
+      <c r="AD16" s="17"/>
+      <c r="AE16" s="17"/>
+      <c r="AF16" s="18"/>
+    </row>
+    <row r="17" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A17" s="17"/>
       <c r="B17" s="17"/>
       <c r="C17" s="17"/>
@@ -1980,13 +2053,16 @@
       <c r="V17" s="19"/>
       <c r="W17" s="19"/>
       <c r="X17" s="19"/>
-      <c r="Y17" s="17"/>
-      <c r="Z17" s="17"/>
+      <c r="Y17" s="19"/>
+      <c r="Z17" s="19"/>
       <c r="AA17" s="17"/>
       <c r="AB17" s="17"/>
-      <c r="AC17" s="18"/>
-    </row>
-    <row r="18" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AC17" s="17"/>
+      <c r="AD17" s="17"/>
+      <c r="AE17" s="17"/>
+      <c r="AF17" s="18"/>
+    </row>
+    <row r="18" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A18" s="17"/>
       <c r="B18" s="17"/>
       <c r="C18" s="17"/>
@@ -2011,13 +2087,16 @@
       <c r="V18" s="19"/>
       <c r="W18" s="19"/>
       <c r="X18" s="19"/>
-      <c r="Y18" s="17"/>
-      <c r="Z18" s="17"/>
+      <c r="Y18" s="19"/>
+      <c r="Z18" s="19"/>
       <c r="AA18" s="17"/>
       <c r="AB18" s="17"/>
-      <c r="AC18" s="18"/>
-    </row>
-    <row r="19" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AC18" s="17"/>
+      <c r="AD18" s="17"/>
+      <c r="AE18" s="17"/>
+      <c r="AF18" s="18"/>
+    </row>
+    <row r="19" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A19" s="17"/>
       <c r="B19" s="17"/>
       <c r="C19" s="17"/>
@@ -2042,13 +2121,16 @@
       <c r="V19" s="19"/>
       <c r="W19" s="19"/>
       <c r="X19" s="19"/>
-      <c r="Y19" s="17"/>
-      <c r="Z19" s="17"/>
+      <c r="Y19" s="19"/>
+      <c r="Z19" s="19"/>
       <c r="AA19" s="17"/>
       <c r="AB19" s="17"/>
-      <c r="AC19" s="18"/>
-    </row>
-    <row r="20" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AC19" s="17"/>
+      <c r="AD19" s="17"/>
+      <c r="AE19" s="17"/>
+      <c r="AF19" s="18"/>
+    </row>
+    <row r="20" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A20" s="17"/>
       <c r="B20" s="17"/>
       <c r="C20" s="17"/>
@@ -2073,13 +2155,16 @@
       <c r="V20" s="19"/>
       <c r="W20" s="19"/>
       <c r="X20" s="19"/>
-      <c r="Y20" s="17"/>
-      <c r="Z20" s="17"/>
+      <c r="Y20" s="19"/>
+      <c r="Z20" s="19"/>
       <c r="AA20" s="17"/>
       <c r="AB20" s="17"/>
-      <c r="AC20" s="18"/>
-    </row>
-    <row r="21" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AC20" s="17"/>
+      <c r="AD20" s="17"/>
+      <c r="AE20" s="17"/>
+      <c r="AF20" s="18"/>
+    </row>
+    <row r="21" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A21" s="17"/>
       <c r="B21" s="17"/>
       <c r="C21" s="17"/>
@@ -2104,13 +2189,16 @@
       <c r="V21" s="19"/>
       <c r="W21" s="19"/>
       <c r="X21" s="19"/>
-      <c r="Y21" s="17"/>
-      <c r="Z21" s="17"/>
+      <c r="Y21" s="19"/>
+      <c r="Z21" s="19"/>
       <c r="AA21" s="17"/>
       <c r="AB21" s="17"/>
-      <c r="AC21" s="18"/>
-    </row>
-    <row r="22" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AC21" s="17"/>
+      <c r="AD21" s="17"/>
+      <c r="AE21" s="17"/>
+      <c r="AF21" s="18"/>
+    </row>
+    <row r="22" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A22" s="17"/>
       <c r="B22" s="17"/>
       <c r="C22" s="17"/>
@@ -2135,13 +2223,16 @@
       <c r="V22" s="19"/>
       <c r="W22" s="19"/>
       <c r="X22" s="19"/>
-      <c r="Y22" s="17"/>
-      <c r="Z22" s="17"/>
+      <c r="Y22" s="19"/>
+      <c r="Z22" s="19"/>
       <c r="AA22" s="17"/>
       <c r="AB22" s="17"/>
-      <c r="AC22" s="18"/>
-    </row>
-    <row r="23" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AC22" s="17"/>
+      <c r="AD22" s="17"/>
+      <c r="AE22" s="17"/>
+      <c r="AF22" s="18"/>
+    </row>
+    <row r="23" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A23" s="17"/>
       <c r="B23" s="17"/>
       <c r="C23" s="17"/>
@@ -2166,13 +2257,16 @@
       <c r="V23" s="19"/>
       <c r="W23" s="19"/>
       <c r="X23" s="19"/>
-      <c r="Y23" s="17"/>
-      <c r="Z23" s="17"/>
+      <c r="Y23" s="19"/>
+      <c r="Z23" s="19"/>
       <c r="AA23" s="17"/>
       <c r="AB23" s="17"/>
-      <c r="AC23" s="18"/>
-    </row>
-    <row r="24" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AC23" s="17"/>
+      <c r="AD23" s="17"/>
+      <c r="AE23" s="17"/>
+      <c r="AF23" s="18"/>
+    </row>
+    <row r="24" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A24" s="17"/>
       <c r="B24" s="17"/>
       <c r="C24" s="17"/>
@@ -2197,13 +2291,16 @@
       <c r="V24" s="19"/>
       <c r="W24" s="19"/>
       <c r="X24" s="19"/>
-      <c r="Y24" s="17"/>
-      <c r="Z24" s="17"/>
+      <c r="Y24" s="19"/>
+      <c r="Z24" s="19"/>
       <c r="AA24" s="17"/>
       <c r="AB24" s="17"/>
-      <c r="AC24" s="18"/>
-    </row>
-    <row r="25" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AC24" s="17"/>
+      <c r="AD24" s="17"/>
+      <c r="AE24" s="17"/>
+      <c r="AF24" s="18"/>
+    </row>
+    <row r="25" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A25" s="17"/>
       <c r="B25" s="17"/>
       <c r="C25" s="17"/>
@@ -2228,13 +2325,16 @@
       <c r="V25" s="19"/>
       <c r="W25" s="19"/>
       <c r="X25" s="19"/>
-      <c r="Y25" s="17"/>
-      <c r="Z25" s="17"/>
+      <c r="Y25" s="19"/>
+      <c r="Z25" s="19"/>
       <c r="AA25" s="17"/>
       <c r="AB25" s="17"/>
-      <c r="AC25" s="18"/>
-    </row>
-    <row r="26" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AC25" s="17"/>
+      <c r="AD25" s="17"/>
+      <c r="AE25" s="17"/>
+      <c r="AF25" s="18"/>
+    </row>
+    <row r="26" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A26" s="17"/>
       <c r="B26" s="17"/>
       <c r="C26" s="17"/>
@@ -2259,13 +2359,16 @@
       <c r="V26" s="19"/>
       <c r="W26" s="19"/>
       <c r="X26" s="19"/>
-      <c r="Y26" s="17"/>
-      <c r="Z26" s="17"/>
+      <c r="Y26" s="19"/>
+      <c r="Z26" s="19"/>
       <c r="AA26" s="17"/>
       <c r="AB26" s="17"/>
-      <c r="AC26" s="18"/>
-    </row>
-    <row r="27" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AC26" s="17"/>
+      <c r="AD26" s="17"/>
+      <c r="AE26" s="17"/>
+      <c r="AF26" s="18"/>
+    </row>
+    <row r="27" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A27" s="17"/>
       <c r="B27" s="17"/>
       <c r="C27" s="17"/>
@@ -2290,13 +2393,16 @@
       <c r="V27" s="19"/>
       <c r="W27" s="19"/>
       <c r="X27" s="19"/>
-      <c r="Y27" s="17"/>
-      <c r="Z27" s="17"/>
+      <c r="Y27" s="19"/>
+      <c r="Z27" s="19"/>
       <c r="AA27" s="17"/>
       <c r="AB27" s="17"/>
-      <c r="AC27" s="18"/>
-    </row>
-    <row r="28" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AC27" s="17"/>
+      <c r="AD27" s="17"/>
+      <c r="AE27" s="17"/>
+      <c r="AF27" s="18"/>
+    </row>
+    <row r="28" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A28" s="17"/>
       <c r="B28" s="17"/>
       <c r="C28" s="17"/>
@@ -2321,13 +2427,16 @@
       <c r="V28" s="19"/>
       <c r="W28" s="19"/>
       <c r="X28" s="19"/>
-      <c r="Y28" s="17"/>
-      <c r="Z28" s="17"/>
+      <c r="Y28" s="19"/>
+      <c r="Z28" s="19"/>
       <c r="AA28" s="17"/>
       <c r="AB28" s="17"/>
-      <c r="AC28" s="18"/>
-    </row>
-    <row r="29" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AC28" s="17"/>
+      <c r="AD28" s="17"/>
+      <c r="AE28" s="17"/>
+      <c r="AF28" s="18"/>
+    </row>
+    <row r="29" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A29" s="17"/>
       <c r="B29" s="17"/>
       <c r="C29" s="17"/>
@@ -2352,13 +2461,16 @@
       <c r="V29" s="19"/>
       <c r="W29" s="19"/>
       <c r="X29" s="19"/>
-      <c r="Y29" s="17"/>
-      <c r="Z29" s="17"/>
+      <c r="Y29" s="19"/>
+      <c r="Z29" s="19"/>
       <c r="AA29" s="17"/>
       <c r="AB29" s="17"/>
-      <c r="AC29" s="18"/>
-    </row>
-    <row r="30" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AC29" s="17"/>
+      <c r="AD29" s="17"/>
+      <c r="AE29" s="17"/>
+      <c r="AF29" s="18"/>
+    </row>
+    <row r="30" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A30" s="17"/>
       <c r="B30" s="17"/>
       <c r="C30" s="17"/>
@@ -2383,13 +2495,16 @@
       <c r="V30" s="19"/>
       <c r="W30" s="19"/>
       <c r="X30" s="19"/>
-      <c r="Y30" s="17"/>
-      <c r="Z30" s="17"/>
+      <c r="Y30" s="19"/>
+      <c r="Z30" s="19"/>
       <c r="AA30" s="17"/>
       <c r="AB30" s="17"/>
-      <c r="AC30" s="18"/>
-    </row>
-    <row r="31" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AC30" s="17"/>
+      <c r="AD30" s="17"/>
+      <c r="AE30" s="17"/>
+      <c r="AF30" s="18"/>
+    </row>
+    <row r="31" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A31" s="17"/>
       <c r="B31" s="17"/>
       <c r="C31" s="17"/>
@@ -2414,13 +2529,16 @@
       <c r="V31" s="19"/>
       <c r="W31" s="19"/>
       <c r="X31" s="19"/>
-      <c r="Y31" s="17"/>
-      <c r="Z31" s="17"/>
+      <c r="Y31" s="19"/>
+      <c r="Z31" s="19"/>
       <c r="AA31" s="17"/>
       <c r="AB31" s="17"/>
-      <c r="AC31" s="18"/>
-    </row>
-    <row r="32" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AC31" s="17"/>
+      <c r="AD31" s="17"/>
+      <c r="AE31" s="17"/>
+      <c r="AF31" s="18"/>
+    </row>
+    <row r="32" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A32" s="17"/>
       <c r="B32" s="17"/>
       <c r="C32" s="17"/>
@@ -2445,13 +2563,16 @@
       <c r="V32" s="19"/>
       <c r="W32" s="19"/>
       <c r="X32" s="19"/>
-      <c r="Y32" s="17"/>
-      <c r="Z32" s="17"/>
+      <c r="Y32" s="19"/>
+      <c r="Z32" s="19"/>
       <c r="AA32" s="17"/>
       <c r="AB32" s="17"/>
-      <c r="AC32" s="18"/>
-    </row>
-    <row r="33" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AC32" s="17"/>
+      <c r="AD32" s="17"/>
+      <c r="AE32" s="17"/>
+      <c r="AF32" s="18"/>
+    </row>
+    <row r="33" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A33" s="17"/>
       <c r="B33" s="17"/>
       <c r="C33" s="17"/>
@@ -2476,13 +2597,16 @@
       <c r="V33" s="19"/>
       <c r="W33" s="19"/>
       <c r="X33" s="19"/>
-      <c r="Y33" s="17"/>
-      <c r="Z33" s="17"/>
+      <c r="Y33" s="19"/>
+      <c r="Z33" s="19"/>
       <c r="AA33" s="17"/>
       <c r="AB33" s="17"/>
-      <c r="AC33" s="18"/>
-    </row>
-    <row r="34" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AC33" s="17"/>
+      <c r="AD33" s="17"/>
+      <c r="AE33" s="17"/>
+      <c r="AF33" s="18"/>
+    </row>
+    <row r="34" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A34" s="17"/>
       <c r="B34" s="17"/>
       <c r="C34" s="17"/>
@@ -2507,13 +2631,16 @@
       <c r="V34" s="19"/>
       <c r="W34" s="19"/>
       <c r="X34" s="19"/>
-      <c r="Y34" s="17"/>
-      <c r="Z34" s="17"/>
+      <c r="Y34" s="19"/>
+      <c r="Z34" s="19"/>
       <c r="AA34" s="17"/>
       <c r="AB34" s="17"/>
-      <c r="AC34" s="18"/>
-    </row>
-    <row r="35" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AC34" s="17"/>
+      <c r="AD34" s="17"/>
+      <c r="AE34" s="17"/>
+      <c r="AF34" s="18"/>
+    </row>
+    <row r="35" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A35" s="17"/>
       <c r="B35" s="17"/>
       <c r="C35" s="17"/>
@@ -2538,13 +2665,16 @@
       <c r="V35" s="19"/>
       <c r="W35" s="19"/>
       <c r="X35" s="19"/>
-      <c r="Y35" s="17"/>
-      <c r="Z35" s="17"/>
+      <c r="Y35" s="19"/>
+      <c r="Z35" s="19"/>
       <c r="AA35" s="17"/>
       <c r="AB35" s="17"/>
-      <c r="AC35" s="18"/>
-    </row>
-    <row r="36" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AC35" s="17"/>
+      <c r="AD35" s="17"/>
+      <c r="AE35" s="17"/>
+      <c r="AF35" s="18"/>
+    </row>
+    <row r="36" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A36" s="17"/>
       <c r="B36" s="17"/>
       <c r="C36" s="17"/>
@@ -2569,13 +2699,16 @@
       <c r="V36" s="19"/>
       <c r="W36" s="19"/>
       <c r="X36" s="19"/>
-      <c r="Y36" s="17"/>
-      <c r="Z36" s="17"/>
+      <c r="Y36" s="19"/>
+      <c r="Z36" s="19"/>
       <c r="AA36" s="17"/>
       <c r="AB36" s="17"/>
-      <c r="AC36" s="18"/>
-    </row>
-    <row r="37" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AC36" s="17"/>
+      <c r="AD36" s="17"/>
+      <c r="AE36" s="17"/>
+      <c r="AF36" s="18"/>
+    </row>
+    <row r="37" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A37" s="17"/>
       <c r="B37" s="17"/>
       <c r="C37" s="17"/>
@@ -2600,13 +2733,16 @@
       <c r="V37" s="19"/>
       <c r="W37" s="19"/>
       <c r="X37" s="19"/>
-      <c r="Y37" s="17"/>
-      <c r="Z37" s="17"/>
+      <c r="Y37" s="19"/>
+      <c r="Z37" s="19"/>
       <c r="AA37" s="17"/>
       <c r="AB37" s="17"/>
-      <c r="AC37" s="18"/>
-    </row>
-    <row r="38" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AC37" s="17"/>
+      <c r="AD37" s="17"/>
+      <c r="AE37" s="17"/>
+      <c r="AF37" s="18"/>
+    </row>
+    <row r="38" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A38" s="17"/>
       <c r="B38" s="17"/>
       <c r="C38" s="17"/>
@@ -2631,13 +2767,16 @@
       <c r="V38" s="19"/>
       <c r="W38" s="19"/>
       <c r="X38" s="19"/>
-      <c r="Y38" s="17"/>
-      <c r="Z38" s="17"/>
+      <c r="Y38" s="19"/>
+      <c r="Z38" s="19"/>
       <c r="AA38" s="17"/>
       <c r="AB38" s="17"/>
-      <c r="AC38" s="18"/>
-    </row>
-    <row r="39" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AC38" s="17"/>
+      <c r="AD38" s="17"/>
+      <c r="AE38" s="17"/>
+      <c r="AF38" s="18"/>
+    </row>
+    <row r="39" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A39" s="17"/>
       <c r="B39" s="17"/>
       <c r="C39" s="17"/>
@@ -2662,13 +2801,16 @@
       <c r="V39" s="19"/>
       <c r="W39" s="19"/>
       <c r="X39" s="19"/>
-      <c r="Y39" s="17"/>
-      <c r="Z39" s="17"/>
+      <c r="Y39" s="19"/>
+      <c r="Z39" s="19"/>
       <c r="AA39" s="17"/>
       <c r="AB39" s="17"/>
-      <c r="AC39" s="18"/>
-    </row>
-    <row r="40" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AC39" s="17"/>
+      <c r="AD39" s="17"/>
+      <c r="AE39" s="17"/>
+      <c r="AF39" s="18"/>
+    </row>
+    <row r="40" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A40" s="17"/>
       <c r="B40" s="17"/>
       <c r="C40" s="17"/>
@@ -2693,13 +2835,16 @@
       <c r="V40" s="19"/>
       <c r="W40" s="19"/>
       <c r="X40" s="19"/>
-      <c r="Y40" s="17"/>
-      <c r="Z40" s="17"/>
+      <c r="Y40" s="19"/>
+      <c r="Z40" s="19"/>
       <c r="AA40" s="17"/>
       <c r="AB40" s="17"/>
-      <c r="AC40" s="18"/>
-    </row>
-    <row r="41" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AC40" s="17"/>
+      <c r="AD40" s="17"/>
+      <c r="AE40" s="17"/>
+      <c r="AF40" s="18"/>
+    </row>
+    <row r="41" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A41" s="17"/>
       <c r="B41" s="17"/>
       <c r="C41" s="17"/>
@@ -2724,13 +2869,16 @@
       <c r="V41" s="19"/>
       <c r="W41" s="19"/>
       <c r="X41" s="19"/>
-      <c r="Y41" s="17"/>
-      <c r="Z41" s="17"/>
+      <c r="Y41" s="19"/>
+      <c r="Z41" s="19"/>
       <c r="AA41" s="17"/>
       <c r="AB41" s="17"/>
-      <c r="AC41" s="18"/>
-    </row>
-    <row r="42" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AC41" s="17"/>
+      <c r="AD41" s="17"/>
+      <c r="AE41" s="17"/>
+      <c r="AF41" s="18"/>
+    </row>
+    <row r="42" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A42" s="17"/>
       <c r="B42" s="17"/>
       <c r="C42" s="17"/>
@@ -2755,13 +2903,16 @@
       <c r="V42" s="19"/>
       <c r="W42" s="19"/>
       <c r="X42" s="19"/>
-      <c r="Y42" s="17"/>
-      <c r="Z42" s="17"/>
+      <c r="Y42" s="19"/>
+      <c r="Z42" s="19"/>
       <c r="AA42" s="17"/>
       <c r="AB42" s="17"/>
-      <c r="AC42" s="18"/>
-    </row>
-    <row r="43" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AC42" s="17"/>
+      <c r="AD42" s="17"/>
+      <c r="AE42" s="17"/>
+      <c r="AF42" s="18"/>
+    </row>
+    <row r="43" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A43" s="17"/>
       <c r="B43" s="17"/>
       <c r="C43" s="17"/>
@@ -2786,13 +2937,16 @@
       <c r="V43" s="19"/>
       <c r="W43" s="19"/>
       <c r="X43" s="19"/>
-      <c r="Y43" s="17"/>
-      <c r="Z43" s="17"/>
+      <c r="Y43" s="19"/>
+      <c r="Z43" s="19"/>
       <c r="AA43" s="17"/>
       <c r="AB43" s="17"/>
-      <c r="AC43" s="18"/>
-    </row>
-    <row r="44" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AC43" s="17"/>
+      <c r="AD43" s="17"/>
+      <c r="AE43" s="17"/>
+      <c r="AF43" s="18"/>
+    </row>
+    <row r="44" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A44" s="17"/>
       <c r="B44" s="17"/>
       <c r="C44" s="17"/>
@@ -2817,13 +2971,16 @@
       <c r="V44" s="19"/>
       <c r="W44" s="19"/>
       <c r="X44" s="19"/>
-      <c r="Y44" s="17"/>
-      <c r="Z44" s="17"/>
+      <c r="Y44" s="19"/>
+      <c r="Z44" s="19"/>
       <c r="AA44" s="17"/>
       <c r="AB44" s="17"/>
-      <c r="AC44" s="18"/>
-    </row>
-    <row r="45" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AC44" s="17"/>
+      <c r="AD44" s="17"/>
+      <c r="AE44" s="17"/>
+      <c r="AF44" s="18"/>
+    </row>
+    <row r="45" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A45" s="17"/>
       <c r="B45" s="17"/>
       <c r="C45" s="17"/>
@@ -2848,13 +3005,16 @@
       <c r="V45" s="19"/>
       <c r="W45" s="19"/>
       <c r="X45" s="19"/>
-      <c r="Y45" s="17"/>
-      <c r="Z45" s="17"/>
+      <c r="Y45" s="19"/>
+      <c r="Z45" s="19"/>
       <c r="AA45" s="17"/>
       <c r="AB45" s="17"/>
-      <c r="AC45" s="18"/>
-    </row>
-    <row r="46" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AC45" s="17"/>
+      <c r="AD45" s="17"/>
+      <c r="AE45" s="17"/>
+      <c r="AF45" s="18"/>
+    </row>
+    <row r="46" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A46" s="17"/>
       <c r="B46" s="17"/>
       <c r="C46" s="17"/>
@@ -2879,13 +3039,16 @@
       <c r="V46" s="19"/>
       <c r="W46" s="19"/>
       <c r="X46" s="19"/>
-      <c r="Y46" s="17"/>
-      <c r="Z46" s="17"/>
+      <c r="Y46" s="19"/>
+      <c r="Z46" s="19"/>
       <c r="AA46" s="17"/>
       <c r="AB46" s="17"/>
-      <c r="AC46" s="18"/>
-    </row>
-    <row r="47" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AC46" s="17"/>
+      <c r="AD46" s="17"/>
+      <c r="AE46" s="17"/>
+      <c r="AF46" s="18"/>
+    </row>
+    <row r="47" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A47" s="17"/>
       <c r="B47" s="17"/>
       <c r="C47" s="17"/>
@@ -2910,13 +3073,16 @@
       <c r="V47" s="19"/>
       <c r="W47" s="19"/>
       <c r="X47" s="19"/>
-      <c r="Y47" s="17"/>
-      <c r="Z47" s="17"/>
+      <c r="Y47" s="19"/>
+      <c r="Z47" s="19"/>
       <c r="AA47" s="17"/>
       <c r="AB47" s="17"/>
-      <c r="AC47" s="18"/>
-    </row>
-    <row r="48" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AC47" s="17"/>
+      <c r="AD47" s="17"/>
+      <c r="AE47" s="17"/>
+      <c r="AF47" s="18"/>
+    </row>
+    <row r="48" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A48" s="17"/>
       <c r="B48" s="17"/>
       <c r="C48" s="17"/>
@@ -2941,13 +3107,16 @@
       <c r="V48" s="19"/>
       <c r="W48" s="19"/>
       <c r="X48" s="19"/>
-      <c r="Y48" s="17"/>
-      <c r="Z48" s="17"/>
+      <c r="Y48" s="19"/>
+      <c r="Z48" s="19"/>
       <c r="AA48" s="17"/>
       <c r="AB48" s="17"/>
-      <c r="AC48" s="18"/>
-    </row>
-    <row r="49" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AC48" s="17"/>
+      <c r="AD48" s="17"/>
+      <c r="AE48" s="17"/>
+      <c r="AF48" s="18"/>
+    </row>
+    <row r="49" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A49" s="17"/>
       <c r="B49" s="17"/>
       <c r="C49" s="17"/>
@@ -2972,13 +3141,16 @@
       <c r="V49" s="19"/>
       <c r="W49" s="19"/>
       <c r="X49" s="19"/>
-      <c r="Y49" s="17"/>
-      <c r="Z49" s="17"/>
+      <c r="Y49" s="19"/>
+      <c r="Z49" s="19"/>
       <c r="AA49" s="17"/>
       <c r="AB49" s="17"/>
-      <c r="AC49" s="18"/>
-    </row>
-    <row r="50" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AC49" s="17"/>
+      <c r="AD49" s="17"/>
+      <c r="AE49" s="17"/>
+      <c r="AF49" s="18"/>
+    </row>
+    <row r="50" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A50" s="17"/>
       <c r="B50" s="17"/>
       <c r="C50" s="17"/>
@@ -3003,13 +3175,16 @@
       <c r="V50" s="19"/>
       <c r="W50" s="19"/>
       <c r="X50" s="19"/>
-      <c r="Y50" s="17"/>
-      <c r="Z50" s="17"/>
+      <c r="Y50" s="19"/>
+      <c r="Z50" s="19"/>
       <c r="AA50" s="17"/>
       <c r="AB50" s="17"/>
-      <c r="AC50" s="18"/>
-    </row>
-    <row r="51" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AC50" s="17"/>
+      <c r="AD50" s="17"/>
+      <c r="AE50" s="17"/>
+      <c r="AF50" s="18"/>
+    </row>
+    <row r="51" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A51" s="17"/>
       <c r="B51" s="17"/>
       <c r="C51" s="17"/>
@@ -3034,13 +3209,16 @@
       <c r="V51" s="19"/>
       <c r="W51" s="19"/>
       <c r="X51" s="19"/>
-      <c r="Y51" s="17"/>
-      <c r="Z51" s="17"/>
+      <c r="Y51" s="19"/>
+      <c r="Z51" s="19"/>
       <c r="AA51" s="17"/>
       <c r="AB51" s="17"/>
-      <c r="AC51" s="18"/>
-    </row>
-    <row r="52" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AC51" s="17"/>
+      <c r="AD51" s="17"/>
+      <c r="AE51" s="17"/>
+      <c r="AF51" s="18"/>
+    </row>
+    <row r="52" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A52" s="17"/>
       <c r="B52" s="17"/>
       <c r="C52" s="17"/>
@@ -3065,13 +3243,16 @@
       <c r="V52" s="19"/>
       <c r="W52" s="19"/>
       <c r="X52" s="19"/>
-      <c r="Y52" s="17"/>
-      <c r="Z52" s="17"/>
+      <c r="Y52" s="19"/>
+      <c r="Z52" s="19"/>
       <c r="AA52" s="17"/>
       <c r="AB52" s="17"/>
-      <c r="AC52" s="18"/>
-    </row>
-    <row r="53" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AC52" s="17"/>
+      <c r="AD52" s="17"/>
+      <c r="AE52" s="17"/>
+      <c r="AF52" s="18"/>
+    </row>
+    <row r="53" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A53" s="17"/>
       <c r="B53" s="17"/>
       <c r="C53" s="17"/>
@@ -3096,13 +3277,16 @@
       <c r="V53" s="19"/>
       <c r="W53" s="19"/>
       <c r="X53" s="19"/>
-      <c r="Y53" s="17"/>
-      <c r="Z53" s="17"/>
+      <c r="Y53" s="19"/>
+      <c r="Z53" s="19"/>
       <c r="AA53" s="17"/>
       <c r="AB53" s="17"/>
-      <c r="AC53" s="18"/>
-    </row>
-    <row r="54" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AC53" s="17"/>
+      <c r="AD53" s="17"/>
+      <c r="AE53" s="17"/>
+      <c r="AF53" s="18"/>
+    </row>
+    <row r="54" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A54" s="17"/>
       <c r="B54" s="17"/>
       <c r="C54" s="17"/>
@@ -3127,13 +3311,16 @@
       <c r="V54" s="19"/>
       <c r="W54" s="19"/>
       <c r="X54" s="19"/>
-      <c r="Y54" s="17"/>
-      <c r="Z54" s="17"/>
+      <c r="Y54" s="19"/>
+      <c r="Z54" s="19"/>
       <c r="AA54" s="17"/>
       <c r="AB54" s="17"/>
-      <c r="AC54" s="18"/>
-    </row>
-    <row r="55" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AC54" s="17"/>
+      <c r="AD54" s="17"/>
+      <c r="AE54" s="17"/>
+      <c r="AF54" s="18"/>
+    </row>
+    <row r="55" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A55" s="17"/>
       <c r="B55" s="17"/>
       <c r="C55" s="17"/>
@@ -3158,13 +3345,16 @@
       <c r="V55" s="19"/>
       <c r="W55" s="19"/>
       <c r="X55" s="19"/>
-      <c r="Y55" s="17"/>
-      <c r="Z55" s="17"/>
+      <c r="Y55" s="19"/>
+      <c r="Z55" s="19"/>
       <c r="AA55" s="17"/>
       <c r="AB55" s="17"/>
-      <c r="AC55" s="18"/>
-    </row>
-    <row r="56" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AC55" s="17"/>
+      <c r="AD55" s="17"/>
+      <c r="AE55" s="17"/>
+      <c r="AF55" s="18"/>
+    </row>
+    <row r="56" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A56" s="17"/>
       <c r="B56" s="17"/>
       <c r="C56" s="17"/>
@@ -3189,13 +3379,16 @@
       <c r="V56" s="19"/>
       <c r="W56" s="19"/>
       <c r="X56" s="19"/>
-      <c r="Y56" s="17"/>
-      <c r="Z56" s="17"/>
+      <c r="Y56" s="19"/>
+      <c r="Z56" s="19"/>
       <c r="AA56" s="17"/>
       <c r="AB56" s="17"/>
-      <c r="AC56" s="18"/>
-    </row>
-    <row r="57" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AC56" s="17"/>
+      <c r="AD56" s="17"/>
+      <c r="AE56" s="17"/>
+      <c r="AF56" s="18"/>
+    </row>
+    <row r="57" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A57" s="17"/>
       <c r="B57" s="17"/>
       <c r="C57" s="17"/>
@@ -3220,13 +3413,16 @@
       <c r="V57" s="19"/>
       <c r="W57" s="19"/>
       <c r="X57" s="19"/>
-      <c r="Y57" s="17"/>
-      <c r="Z57" s="17"/>
+      <c r="Y57" s="19"/>
+      <c r="Z57" s="19"/>
       <c r="AA57" s="17"/>
       <c r="AB57" s="17"/>
-      <c r="AC57" s="18"/>
-    </row>
-    <row r="58" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AC57" s="17"/>
+      <c r="AD57" s="17"/>
+      <c r="AE57" s="17"/>
+      <c r="AF57" s="18"/>
+    </row>
+    <row r="58" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A58" s="17"/>
       <c r="B58" s="17"/>
       <c r="C58" s="17"/>
@@ -3251,13 +3447,16 @@
       <c r="V58" s="19"/>
       <c r="W58" s="19"/>
       <c r="X58" s="19"/>
-      <c r="Y58" s="17"/>
-      <c r="Z58" s="17"/>
+      <c r="Y58" s="19"/>
+      <c r="Z58" s="19"/>
       <c r="AA58" s="17"/>
       <c r="AB58" s="17"/>
-      <c r="AC58" s="18"/>
-    </row>
-    <row r="59" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AC58" s="17"/>
+      <c r="AD58" s="17"/>
+      <c r="AE58" s="17"/>
+      <c r="AF58" s="18"/>
+    </row>
+    <row r="59" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A59" s="17"/>
       <c r="B59" s="17"/>
       <c r="C59" s="17"/>
@@ -3282,13 +3481,16 @@
       <c r="V59" s="19"/>
       <c r="W59" s="19"/>
       <c r="X59" s="19"/>
-      <c r="Y59" s="17"/>
-      <c r="Z59" s="17"/>
+      <c r="Y59" s="19"/>
+      <c r="Z59" s="19"/>
       <c r="AA59" s="17"/>
       <c r="AB59" s="17"/>
-      <c r="AC59" s="18"/>
-    </row>
-    <row r="60" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AC59" s="17"/>
+      <c r="AD59" s="17"/>
+      <c r="AE59" s="17"/>
+      <c r="AF59" s="18"/>
+    </row>
+    <row r="60" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A60" s="17"/>
       <c r="B60" s="17"/>
       <c r="C60" s="17"/>
@@ -3313,13 +3515,16 @@
       <c r="V60" s="19"/>
       <c r="W60" s="19"/>
       <c r="X60" s="19"/>
-      <c r="Y60" s="17"/>
-      <c r="Z60" s="17"/>
+      <c r="Y60" s="19"/>
+      <c r="Z60" s="19"/>
       <c r="AA60" s="17"/>
       <c r="AB60" s="17"/>
-      <c r="AC60" s="18"/>
-    </row>
-    <row r="61" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AC60" s="17"/>
+      <c r="AD60" s="17"/>
+      <c r="AE60" s="17"/>
+      <c r="AF60" s="18"/>
+    </row>
+    <row r="61" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A61" s="17"/>
       <c r="B61" s="17"/>
       <c r="C61" s="17"/>
@@ -3344,13 +3549,16 @@
       <c r="V61" s="19"/>
       <c r="W61" s="19"/>
       <c r="X61" s="19"/>
-      <c r="Y61" s="17"/>
-      <c r="Z61" s="17"/>
+      <c r="Y61" s="19"/>
+      <c r="Z61" s="19"/>
       <c r="AA61" s="17"/>
       <c r="AB61" s="17"/>
-      <c r="AC61" s="18"/>
-    </row>
-    <row r="62" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AC61" s="17"/>
+      <c r="AD61" s="17"/>
+      <c r="AE61" s="17"/>
+      <c r="AF61" s="18"/>
+    </row>
+    <row r="62" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A62" s="17"/>
       <c r="B62" s="17"/>
       <c r="C62" s="17"/>
@@ -3375,13 +3583,16 @@
       <c r="V62" s="19"/>
       <c r="W62" s="19"/>
       <c r="X62" s="19"/>
-      <c r="Y62" s="17"/>
-      <c r="Z62" s="17"/>
+      <c r="Y62" s="19"/>
+      <c r="Z62" s="19"/>
       <c r="AA62" s="17"/>
       <c r="AB62" s="17"/>
-      <c r="AC62" s="18"/>
-    </row>
-    <row r="63" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AC62" s="17"/>
+      <c r="AD62" s="17"/>
+      <c r="AE62" s="17"/>
+      <c r="AF62" s="18"/>
+    </row>
+    <row r="63" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A63" s="17"/>
       <c r="B63" s="17"/>
       <c r="C63" s="17"/>
@@ -3406,13 +3617,16 @@
       <c r="V63" s="19"/>
       <c r="W63" s="19"/>
       <c r="X63" s="19"/>
-      <c r="Y63" s="17"/>
-      <c r="Z63" s="17"/>
+      <c r="Y63" s="19"/>
+      <c r="Z63" s="19"/>
       <c r="AA63" s="17"/>
       <c r="AB63" s="17"/>
-      <c r="AC63" s="18"/>
-    </row>
-    <row r="64" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AC63" s="17"/>
+      <c r="AD63" s="17"/>
+      <c r="AE63" s="17"/>
+      <c r="AF63" s="18"/>
+    </row>
+    <row r="64" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A64" s="17"/>
       <c r="B64" s="17"/>
       <c r="C64" s="17"/>
@@ -3437,13 +3651,16 @@
       <c r="V64" s="19"/>
       <c r="W64" s="19"/>
       <c r="X64" s="19"/>
-      <c r="Y64" s="17"/>
-      <c r="Z64" s="17"/>
+      <c r="Y64" s="19"/>
+      <c r="Z64" s="19"/>
       <c r="AA64" s="17"/>
       <c r="AB64" s="17"/>
-      <c r="AC64" s="18"/>
-    </row>
-    <row r="65" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AC64" s="17"/>
+      <c r="AD64" s="17"/>
+      <c r="AE64" s="17"/>
+      <c r="AF64" s="18"/>
+    </row>
+    <row r="65" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A65" s="17"/>
       <c r="B65" s="17"/>
       <c r="C65" s="17"/>
@@ -3468,13 +3685,16 @@
       <c r="V65" s="19"/>
       <c r="W65" s="19"/>
       <c r="X65" s="19"/>
-      <c r="Y65" s="17"/>
-      <c r="Z65" s="17"/>
+      <c r="Y65" s="19"/>
+      <c r="Z65" s="19"/>
       <c r="AA65" s="17"/>
       <c r="AB65" s="17"/>
-      <c r="AC65" s="18"/>
-    </row>
-    <row r="66" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AC65" s="17"/>
+      <c r="AD65" s="17"/>
+      <c r="AE65" s="17"/>
+      <c r="AF65" s="18"/>
+    </row>
+    <row r="66" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A66" s="17"/>
       <c r="B66" s="17"/>
       <c r="C66" s="17"/>
@@ -3499,13 +3719,16 @@
       <c r="V66" s="19"/>
       <c r="W66" s="19"/>
       <c r="X66" s="19"/>
-      <c r="Y66" s="17"/>
-      <c r="Z66" s="17"/>
+      <c r="Y66" s="19"/>
+      <c r="Z66" s="19"/>
       <c r="AA66" s="17"/>
       <c r="AB66" s="17"/>
-      <c r="AC66" s="18"/>
-    </row>
-    <row r="67" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AC66" s="17"/>
+      <c r="AD66" s="17"/>
+      <c r="AE66" s="17"/>
+      <c r="AF66" s="18"/>
+    </row>
+    <row r="67" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A67" s="17"/>
       <c r="B67" s="17"/>
       <c r="C67" s="17"/>
@@ -3530,13 +3753,16 @@
       <c r="V67" s="19"/>
       <c r="W67" s="19"/>
       <c r="X67" s="19"/>
-      <c r="Y67" s="17"/>
-      <c r="Z67" s="17"/>
+      <c r="Y67" s="19"/>
+      <c r="Z67" s="19"/>
       <c r="AA67" s="17"/>
       <c r="AB67" s="17"/>
-      <c r="AC67" s="18"/>
-    </row>
-    <row r="68" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AC67" s="17"/>
+      <c r="AD67" s="17"/>
+      <c r="AE67" s="17"/>
+      <c r="AF67" s="18"/>
+    </row>
+    <row r="68" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A68" s="17"/>
       <c r="B68" s="17"/>
       <c r="C68" s="17"/>
@@ -3561,13 +3787,16 @@
       <c r="V68" s="19"/>
       <c r="W68" s="19"/>
       <c r="X68" s="19"/>
-      <c r="Y68" s="17"/>
-      <c r="Z68" s="17"/>
+      <c r="Y68" s="19"/>
+      <c r="Z68" s="19"/>
       <c r="AA68" s="17"/>
       <c r="AB68" s="17"/>
-      <c r="AC68" s="18"/>
-    </row>
-    <row r="69" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AC68" s="17"/>
+      <c r="AD68" s="17"/>
+      <c r="AE68" s="17"/>
+      <c r="AF68" s="18"/>
+    </row>
+    <row r="69" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A69" s="17"/>
       <c r="B69" s="17"/>
       <c r="C69" s="17"/>
@@ -3592,13 +3821,16 @@
       <c r="V69" s="19"/>
       <c r="W69" s="19"/>
       <c r="X69" s="19"/>
-      <c r="Y69" s="17"/>
-      <c r="Z69" s="17"/>
+      <c r="Y69" s="19"/>
+      <c r="Z69" s="19"/>
       <c r="AA69" s="17"/>
       <c r="AB69" s="17"/>
-      <c r="AC69" s="18"/>
-    </row>
-    <row r="70" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AC69" s="17"/>
+      <c r="AD69" s="17"/>
+      <c r="AE69" s="17"/>
+      <c r="AF69" s="18"/>
+    </row>
+    <row r="70" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A70" s="17"/>
       <c r="B70" s="17"/>
       <c r="C70" s="17"/>
@@ -3623,13 +3855,16 @@
       <c r="V70" s="19"/>
       <c r="W70" s="19"/>
       <c r="X70" s="19"/>
-      <c r="Y70" s="17"/>
-      <c r="Z70" s="17"/>
+      <c r="Y70" s="19"/>
+      <c r="Z70" s="19"/>
       <c r="AA70" s="17"/>
       <c r="AB70" s="17"/>
-      <c r="AC70" s="18"/>
-    </row>
-    <row r="71" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AC70" s="17"/>
+      <c r="AD70" s="17"/>
+      <c r="AE70" s="17"/>
+      <c r="AF70" s="18"/>
+    </row>
+    <row r="71" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A71" s="17"/>
       <c r="B71" s="17"/>
       <c r="C71" s="17"/>
@@ -3654,13 +3889,16 @@
       <c r="V71" s="19"/>
       <c r="W71" s="19"/>
       <c r="X71" s="19"/>
-      <c r="Y71" s="17"/>
-      <c r="Z71" s="17"/>
+      <c r="Y71" s="19"/>
+      <c r="Z71" s="19"/>
       <c r="AA71" s="17"/>
       <c r="AB71" s="17"/>
-      <c r="AC71" s="18"/>
-    </row>
-    <row r="72" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AC71" s="17"/>
+      <c r="AD71" s="17"/>
+      <c r="AE71" s="17"/>
+      <c r="AF71" s="18"/>
+    </row>
+    <row r="72" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A72" s="17"/>
       <c r="B72" s="17"/>
       <c r="C72" s="17"/>
@@ -3685,13 +3923,16 @@
       <c r="V72" s="19"/>
       <c r="W72" s="19"/>
       <c r="X72" s="19"/>
-      <c r="Y72" s="17"/>
-      <c r="Z72" s="17"/>
+      <c r="Y72" s="19"/>
+      <c r="Z72" s="19"/>
       <c r="AA72" s="17"/>
       <c r="AB72" s="17"/>
-      <c r="AC72" s="18"/>
-    </row>
-    <row r="73" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AC72" s="17"/>
+      <c r="AD72" s="17"/>
+      <c r="AE72" s="17"/>
+      <c r="AF72" s="18"/>
+    </row>
+    <row r="73" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A73" s="17"/>
       <c r="B73" s="17"/>
       <c r="C73" s="17"/>
@@ -3716,13 +3957,16 @@
       <c r="V73" s="19"/>
       <c r="W73" s="19"/>
       <c r="X73" s="19"/>
-      <c r="Y73" s="17"/>
-      <c r="Z73" s="17"/>
+      <c r="Y73" s="19"/>
+      <c r="Z73" s="19"/>
       <c r="AA73" s="17"/>
       <c r="AB73" s="17"/>
-      <c r="AC73" s="18"/>
-    </row>
-    <row r="74" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AC73" s="17"/>
+      <c r="AD73" s="17"/>
+      <c r="AE73" s="17"/>
+      <c r="AF73" s="18"/>
+    </row>
+    <row r="74" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A74" s="17"/>
       <c r="B74" s="17"/>
       <c r="C74" s="17"/>
@@ -3747,13 +3991,16 @@
       <c r="V74" s="19"/>
       <c r="W74" s="19"/>
       <c r="X74" s="19"/>
-      <c r="Y74" s="17"/>
-      <c r="Z74" s="17"/>
+      <c r="Y74" s="19"/>
+      <c r="Z74" s="19"/>
       <c r="AA74" s="17"/>
       <c r="AB74" s="17"/>
-      <c r="AC74" s="18"/>
-    </row>
-    <row r="75" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AC74" s="17"/>
+      <c r="AD74" s="17"/>
+      <c r="AE74" s="17"/>
+      <c r="AF74" s="18"/>
+    </row>
+    <row r="75" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A75" s="17"/>
       <c r="B75" s="17"/>
       <c r="C75" s="17"/>
@@ -3778,13 +4025,16 @@
       <c r="V75" s="19"/>
       <c r="W75" s="19"/>
       <c r="X75" s="19"/>
-      <c r="Y75" s="17"/>
-      <c r="Z75" s="17"/>
+      <c r="Y75" s="19"/>
+      <c r="Z75" s="19"/>
       <c r="AA75" s="17"/>
       <c r="AB75" s="17"/>
-      <c r="AC75" s="18"/>
-    </row>
-    <row r="76" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AC75" s="17"/>
+      <c r="AD75" s="17"/>
+      <c r="AE75" s="17"/>
+      <c r="AF75" s="18"/>
+    </row>
+    <row r="76" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A76" s="17"/>
       <c r="B76" s="17"/>
       <c r="C76" s="17"/>
@@ -3809,13 +4059,16 @@
       <c r="V76" s="19"/>
       <c r="W76" s="19"/>
       <c r="X76" s="19"/>
-      <c r="Y76" s="17"/>
-      <c r="Z76" s="17"/>
+      <c r="Y76" s="19"/>
+      <c r="Z76" s="19"/>
       <c r="AA76" s="17"/>
       <c r="AB76" s="17"/>
-      <c r="AC76" s="18"/>
-    </row>
-    <row r="77" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AC76" s="17"/>
+      <c r="AD76" s="17"/>
+      <c r="AE76" s="17"/>
+      <c r="AF76" s="18"/>
+    </row>
+    <row r="77" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A77" s="17"/>
       <c r="B77" s="17"/>
       <c r="C77" s="17"/>
@@ -3840,19 +4093,22 @@
       <c r="V77" s="19"/>
       <c r="W77" s="19"/>
       <c r="X77" s="19"/>
-      <c r="Y77" s="17"/>
-      <c r="Z77" s="17"/>
+      <c r="Y77" s="19"/>
+      <c r="Z77" s="19"/>
       <c r="AA77" s="17"/>
       <c r="AB77" s="17"/>
-      <c r="AC77" s="18"/>
+      <c r="AC77" s="17"/>
+      <c r="AD77" s="17"/>
+      <c r="AE77" s="17"/>
+      <c r="AF77" s="18"/>
     </row>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="A4:X4"/>
-    <mergeCell ref="A9:X9"/>
+    <mergeCell ref="A4:Z4"/>
+    <mergeCell ref="A9:Z9"/>
     <mergeCell ref="A10:J10"/>
-    <mergeCell ref="K10:X10"/>
-    <mergeCell ref="Y10:AC10"/>
+    <mergeCell ref="K10:Z10"/>
+    <mergeCell ref="AA10:AF10"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="V13:V77" xr:uid="{7A47D03C-AF0D-4783-9711-7BE1E853739B}">

--- a/wwwroot/template/TmSendMailNew.xlsx
+++ b/wwwroot/template/TmSendMailNew.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\khanhmf\Cost Managerment\wwwroot\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73B94A57-874D-4FFF-93BD-5D4A623E828D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4526F9A9-069C-4A60-BA0A-F46ABB747F1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{2DA54543-7852-4C3B-B81A-134334FCB771}"/>
   </bookViews>
@@ -95,7 +95,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="159">
   <si>
     <t>Company name</t>
   </si>
@@ -591,6 +591,9 @@
   </si>
   <si>
     <t>Expiration date of the price</t>
+  </si>
+  <si>
+    <t>Name IMG or Design file</t>
   </si>
 </sst>
 </file>
@@ -1216,7 +1219,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{612B90E7-BC5D-4BEC-8F3F-8E9549A9E0DD}">
-  <dimension ref="A1:AR77"/>
+  <dimension ref="A1:AS77"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="12.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="15" width="8.7109375" style="1"/>
@@ -1230,7 +1233,7 @@
     <col min="31" max="16384" width="8.7109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:44" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:45" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1277,8 +1280,9 @@
       <c r="AN1" s="1"/>
       <c r="AO1" s="1"/>
       <c r="AP1" s="1"/>
-    </row>
-    <row r="2" spans="1:44" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="AQ1" s="1"/>
+    </row>
+    <row r="2" spans="1:45" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -1325,8 +1329,9 @@
       <c r="AN2" s="1"/>
       <c r="AO2" s="1"/>
       <c r="AP2" s="1"/>
-    </row>
-    <row r="3" spans="1:44" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="AQ2" s="1"/>
+    </row>
+    <row r="3" spans="1:45" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
@@ -1371,8 +1376,9 @@
       <c r="AN3" s="1"/>
       <c r="AO3" s="1"/>
       <c r="AP3" s="1"/>
-    </row>
-    <row r="4" spans="1:44" s="5" customFormat="1" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="AQ3" s="1"/>
+    </row>
+    <row r="4" spans="1:45" s="5" customFormat="1" ht="18.75" x14ac:dyDescent="0.2">
       <c r="A4" s="27" t="s">
         <v>4</v>
       </c>
@@ -1417,8 +1423,9 @@
       <c r="AN4" s="1"/>
       <c r="AO4" s="1"/>
       <c r="AP4" s="1"/>
-    </row>
-    <row r="5" spans="1:44" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="AQ4" s="1"/>
+    </row>
+    <row r="5" spans="1:45" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
@@ -1467,8 +1474,9 @@
       <c r="AN5" s="1"/>
       <c r="AO5" s="1"/>
       <c r="AP5" s="1"/>
-    </row>
-    <row r="6" spans="1:44" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="AQ5" s="1"/>
+    </row>
+    <row r="6" spans="1:45" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A6" s="1"/>
       <c r="B6" s="1" t="s">
         <v>8</v>
@@ -1515,8 +1523,9 @@
       <c r="AN6" s="1"/>
       <c r="AO6" s="1"/>
       <c r="AP6" s="1"/>
-    </row>
-    <row r="7" spans="1:44" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="AQ6" s="1"/>
+    </row>
+    <row r="7" spans="1:45" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A7" s="1"/>
       <c r="B7" s="1" t="s">
         <v>10</v>
@@ -1563,8 +1572,9 @@
       <c r="AN7" s="1"/>
       <c r="AO7" s="1"/>
       <c r="AP7" s="1"/>
-    </row>
-    <row r="8" spans="1:44" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="AQ7" s="1"/>
+    </row>
+    <row r="8" spans="1:45" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
@@ -1607,8 +1617,9 @@
       <c r="AN8" s="1"/>
       <c r="AO8" s="1"/>
       <c r="AP8" s="1"/>
-    </row>
-    <row r="9" spans="1:44" s="5" customFormat="1" ht="66" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AQ8" s="1"/>
+    </row>
+    <row r="9" spans="1:45" s="5" customFormat="1" ht="66" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="28" t="s">
         <v>12</v>
       </c>
@@ -1655,8 +1666,9 @@
       <c r="AP9" s="10"/>
       <c r="AQ9" s="10"/>
       <c r="AR9" s="10"/>
-    </row>
-    <row r="10" spans="1:44" ht="73.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AS9" s="10"/>
+    </row>
+    <row r="10" spans="1:45" ht="73.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="29" t="s">
         <v>13</v>
       </c>
@@ -1695,8 +1707,9 @@
       <c r="AD10" s="33"/>
       <c r="AE10" s="33"/>
       <c r="AF10" s="33"/>
-    </row>
-    <row r="11" spans="1:44" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AG10" s="33"/>
+    </row>
+    <row r="11" spans="1:45" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="11">
         <v>1</v>
       </c>
@@ -1793,8 +1806,11 @@
       <c r="AF11" s="11">
         <v>32</v>
       </c>
-    </row>
-    <row r="12" spans="1:44" ht="76.5" x14ac:dyDescent="0.25">
+      <c r="AG11" s="11">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="12" spans="1:45" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
         <v>16</v>
       </c>
@@ -1891,8 +1907,11 @@
       <c r="AF12" s="13" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="13" spans="1:44" x14ac:dyDescent="0.25">
+      <c r="AG12" s="13" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="13" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A13" s="17"/>
       <c r="B13" s="17"/>
       <c r="C13" s="17"/>
@@ -1925,8 +1944,9 @@
       <c r="AD13" s="17"/>
       <c r="AE13" s="17"/>
       <c r="AF13" s="18"/>
-    </row>
-    <row r="14" spans="1:44" x14ac:dyDescent="0.25">
+      <c r="AG13" s="17"/>
+    </row>
+    <row r="14" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A14" s="17"/>
       <c r="B14" s="17"/>
       <c r="C14" s="17"/>
@@ -1959,8 +1979,9 @@
       <c r="AD14" s="17"/>
       <c r="AE14" s="17"/>
       <c r="AF14" s="18"/>
-    </row>
-    <row r="15" spans="1:44" x14ac:dyDescent="0.25">
+      <c r="AG14" s="17"/>
+    </row>
+    <row r="15" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A15" s="17"/>
       <c r="B15" s="17"/>
       <c r="C15" s="17"/>
@@ -1993,8 +2014,9 @@
       <c r="AD15" s="17"/>
       <c r="AE15" s="17"/>
       <c r="AF15" s="18"/>
-    </row>
-    <row r="16" spans="1:44" x14ac:dyDescent="0.25">
+      <c r="AG15" s="17"/>
+    </row>
+    <row r="16" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A16" s="17"/>
       <c r="B16" s="17"/>
       <c r="C16" s="17"/>
@@ -2027,8 +2049,9 @@
       <c r="AD16" s="17"/>
       <c r="AE16" s="17"/>
       <c r="AF16" s="18"/>
-    </row>
-    <row r="17" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AG16" s="17"/>
+    </row>
+    <row r="17" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A17" s="17"/>
       <c r="B17" s="17"/>
       <c r="C17" s="17"/>
@@ -2061,8 +2084,9 @@
       <c r="AD17" s="17"/>
       <c r="AE17" s="17"/>
       <c r="AF17" s="18"/>
-    </row>
-    <row r="18" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AG17" s="17"/>
+    </row>
+    <row r="18" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A18" s="17"/>
       <c r="B18" s="17"/>
       <c r="C18" s="17"/>
@@ -2095,8 +2119,9 @@
       <c r="AD18" s="17"/>
       <c r="AE18" s="17"/>
       <c r="AF18" s="18"/>
-    </row>
-    <row r="19" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AG18" s="17"/>
+    </row>
+    <row r="19" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A19" s="17"/>
       <c r="B19" s="17"/>
       <c r="C19" s="17"/>
@@ -2129,8 +2154,9 @@
       <c r="AD19" s="17"/>
       <c r="AE19" s="17"/>
       <c r="AF19" s="18"/>
-    </row>
-    <row r="20" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AG19" s="17"/>
+    </row>
+    <row r="20" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A20" s="17"/>
       <c r="B20" s="17"/>
       <c r="C20" s="17"/>
@@ -2163,8 +2189,9 @@
       <c r="AD20" s="17"/>
       <c r="AE20" s="17"/>
       <c r="AF20" s="18"/>
-    </row>
-    <row r="21" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AG20" s="17"/>
+    </row>
+    <row r="21" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A21" s="17"/>
       <c r="B21" s="17"/>
       <c r="C21" s="17"/>
@@ -2197,8 +2224,9 @@
       <c r="AD21" s="17"/>
       <c r="AE21" s="17"/>
       <c r="AF21" s="18"/>
-    </row>
-    <row r="22" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AG21" s="17"/>
+    </row>
+    <row r="22" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A22" s="17"/>
       <c r="B22" s="17"/>
       <c r="C22" s="17"/>
@@ -2231,8 +2259,9 @@
       <c r="AD22" s="17"/>
       <c r="AE22" s="17"/>
       <c r="AF22" s="18"/>
-    </row>
-    <row r="23" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AG22" s="17"/>
+    </row>
+    <row r="23" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A23" s="17"/>
       <c r="B23" s="17"/>
       <c r="C23" s="17"/>
@@ -2265,8 +2294,9 @@
       <c r="AD23" s="17"/>
       <c r="AE23" s="17"/>
       <c r="AF23" s="18"/>
-    </row>
-    <row r="24" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AG23" s="17"/>
+    </row>
+    <row r="24" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A24" s="17"/>
       <c r="B24" s="17"/>
       <c r="C24" s="17"/>
@@ -2299,8 +2329,9 @@
       <c r="AD24" s="17"/>
       <c r="AE24" s="17"/>
       <c r="AF24" s="18"/>
-    </row>
-    <row r="25" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AG24" s="17"/>
+    </row>
+    <row r="25" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A25" s="17"/>
       <c r="B25" s="17"/>
       <c r="C25" s="17"/>
@@ -2333,8 +2364,9 @@
       <c r="AD25" s="17"/>
       <c r="AE25" s="17"/>
       <c r="AF25" s="18"/>
-    </row>
-    <row r="26" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AG25" s="17"/>
+    </row>
+    <row r="26" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A26" s="17"/>
       <c r="B26" s="17"/>
       <c r="C26" s="17"/>
@@ -2367,8 +2399,9 @@
       <c r="AD26" s="17"/>
       <c r="AE26" s="17"/>
       <c r="AF26" s="18"/>
-    </row>
-    <row r="27" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AG26" s="17"/>
+    </row>
+    <row r="27" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A27" s="17"/>
       <c r="B27" s="17"/>
       <c r="C27" s="17"/>
@@ -2401,8 +2434,9 @@
       <c r="AD27" s="17"/>
       <c r="AE27" s="17"/>
       <c r="AF27" s="18"/>
-    </row>
-    <row r="28" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AG27" s="17"/>
+    </row>
+    <row r="28" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A28" s="17"/>
       <c r="B28" s="17"/>
       <c r="C28" s="17"/>
@@ -2435,8 +2469,9 @@
       <c r="AD28" s="17"/>
       <c r="AE28" s="17"/>
       <c r="AF28" s="18"/>
-    </row>
-    <row r="29" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AG28" s="17"/>
+    </row>
+    <row r="29" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A29" s="17"/>
       <c r="B29" s="17"/>
       <c r="C29" s="17"/>
@@ -2469,8 +2504,9 @@
       <c r="AD29" s="17"/>
       <c r="AE29" s="17"/>
       <c r="AF29" s="18"/>
-    </row>
-    <row r="30" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AG29" s="17"/>
+    </row>
+    <row r="30" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A30" s="17"/>
       <c r="B30" s="17"/>
       <c r="C30" s="17"/>
@@ -2503,8 +2539,9 @@
       <c r="AD30" s="17"/>
       <c r="AE30" s="17"/>
       <c r="AF30" s="18"/>
-    </row>
-    <row r="31" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AG30" s="17"/>
+    </row>
+    <row r="31" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A31" s="17"/>
       <c r="B31" s="17"/>
       <c r="C31" s="17"/>
@@ -2537,8 +2574,9 @@
       <c r="AD31" s="17"/>
       <c r="AE31" s="17"/>
       <c r="AF31" s="18"/>
-    </row>
-    <row r="32" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AG31" s="17"/>
+    </row>
+    <row r="32" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A32" s="17"/>
       <c r="B32" s="17"/>
       <c r="C32" s="17"/>
@@ -2571,8 +2609,9 @@
       <c r="AD32" s="17"/>
       <c r="AE32" s="17"/>
       <c r="AF32" s="18"/>
-    </row>
-    <row r="33" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AG32" s="17"/>
+    </row>
+    <row r="33" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A33" s="17"/>
       <c r="B33" s="17"/>
       <c r="C33" s="17"/>
@@ -2605,8 +2644,9 @@
       <c r="AD33" s="17"/>
       <c r="AE33" s="17"/>
       <c r="AF33" s="18"/>
-    </row>
-    <row r="34" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AG33" s="17"/>
+    </row>
+    <row r="34" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A34" s="17"/>
       <c r="B34" s="17"/>
       <c r="C34" s="17"/>
@@ -2639,8 +2679,9 @@
       <c r="AD34" s="17"/>
       <c r="AE34" s="17"/>
       <c r="AF34" s="18"/>
-    </row>
-    <row r="35" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AG34" s="17"/>
+    </row>
+    <row r="35" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A35" s="17"/>
       <c r="B35" s="17"/>
       <c r="C35" s="17"/>
@@ -2673,8 +2714,9 @@
       <c r="AD35" s="17"/>
       <c r="AE35" s="17"/>
       <c r="AF35" s="18"/>
-    </row>
-    <row r="36" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AG35" s="17"/>
+    </row>
+    <row r="36" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A36" s="17"/>
       <c r="B36" s="17"/>
       <c r="C36" s="17"/>
@@ -2707,8 +2749,9 @@
       <c r="AD36" s="17"/>
       <c r="AE36" s="17"/>
       <c r="AF36" s="18"/>
-    </row>
-    <row r="37" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AG36" s="17"/>
+    </row>
+    <row r="37" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A37" s="17"/>
       <c r="B37" s="17"/>
       <c r="C37" s="17"/>
@@ -2741,8 +2784,9 @@
       <c r="AD37" s="17"/>
       <c r="AE37" s="17"/>
       <c r="AF37" s="18"/>
-    </row>
-    <row r="38" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AG37" s="17"/>
+    </row>
+    <row r="38" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A38" s="17"/>
       <c r="B38" s="17"/>
       <c r="C38" s="17"/>
@@ -2775,8 +2819,9 @@
       <c r="AD38" s="17"/>
       <c r="AE38" s="17"/>
       <c r="AF38" s="18"/>
-    </row>
-    <row r="39" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AG38" s="17"/>
+    </row>
+    <row r="39" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A39" s="17"/>
       <c r="B39" s="17"/>
       <c r="C39" s="17"/>
@@ -2809,8 +2854,9 @@
       <c r="AD39" s="17"/>
       <c r="AE39" s="17"/>
       <c r="AF39" s="18"/>
-    </row>
-    <row r="40" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AG39" s="17"/>
+    </row>
+    <row r="40" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A40" s="17"/>
       <c r="B40" s="17"/>
       <c r="C40" s="17"/>
@@ -2843,8 +2889,9 @@
       <c r="AD40" s="17"/>
       <c r="AE40" s="17"/>
       <c r="AF40" s="18"/>
-    </row>
-    <row r="41" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AG40" s="17"/>
+    </row>
+    <row r="41" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A41" s="17"/>
       <c r="B41" s="17"/>
       <c r="C41" s="17"/>
@@ -2877,8 +2924,9 @@
       <c r="AD41" s="17"/>
       <c r="AE41" s="17"/>
       <c r="AF41" s="18"/>
-    </row>
-    <row r="42" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AG41" s="17"/>
+    </row>
+    <row r="42" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A42" s="17"/>
       <c r="B42" s="17"/>
       <c r="C42" s="17"/>
@@ -2911,8 +2959,9 @@
       <c r="AD42" s="17"/>
       <c r="AE42" s="17"/>
       <c r="AF42" s="18"/>
-    </row>
-    <row r="43" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AG42" s="17"/>
+    </row>
+    <row r="43" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A43" s="17"/>
       <c r="B43" s="17"/>
       <c r="C43" s="17"/>
@@ -2945,8 +2994,9 @@
       <c r="AD43" s="17"/>
       <c r="AE43" s="17"/>
       <c r="AF43" s="18"/>
-    </row>
-    <row r="44" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AG43" s="17"/>
+    </row>
+    <row r="44" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A44" s="17"/>
       <c r="B44" s="17"/>
       <c r="C44" s="17"/>
@@ -2979,8 +3029,9 @@
       <c r="AD44" s="17"/>
       <c r="AE44" s="17"/>
       <c r="AF44" s="18"/>
-    </row>
-    <row r="45" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AG44" s="17"/>
+    </row>
+    <row r="45" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A45" s="17"/>
       <c r="B45" s="17"/>
       <c r="C45" s="17"/>
@@ -3013,8 +3064,9 @@
       <c r="AD45" s="17"/>
       <c r="AE45" s="17"/>
       <c r="AF45" s="18"/>
-    </row>
-    <row r="46" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AG45" s="17"/>
+    </row>
+    <row r="46" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A46" s="17"/>
       <c r="B46" s="17"/>
       <c r="C46" s="17"/>
@@ -3047,8 +3099,9 @@
       <c r="AD46" s="17"/>
       <c r="AE46" s="17"/>
       <c r="AF46" s="18"/>
-    </row>
-    <row r="47" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AG46" s="17"/>
+    </row>
+    <row r="47" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A47" s="17"/>
       <c r="B47" s="17"/>
       <c r="C47" s="17"/>
@@ -3081,8 +3134,9 @@
       <c r="AD47" s="17"/>
       <c r="AE47" s="17"/>
       <c r="AF47" s="18"/>
-    </row>
-    <row r="48" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AG47" s="17"/>
+    </row>
+    <row r="48" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A48" s="17"/>
       <c r="B48" s="17"/>
       <c r="C48" s="17"/>
@@ -3115,8 +3169,9 @@
       <c r="AD48" s="17"/>
       <c r="AE48" s="17"/>
       <c r="AF48" s="18"/>
-    </row>
-    <row r="49" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AG48" s="17"/>
+    </row>
+    <row r="49" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A49" s="17"/>
       <c r="B49" s="17"/>
       <c r="C49" s="17"/>
@@ -3149,8 +3204,9 @@
       <c r="AD49" s="17"/>
       <c r="AE49" s="17"/>
       <c r="AF49" s="18"/>
-    </row>
-    <row r="50" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AG49" s="17"/>
+    </row>
+    <row r="50" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A50" s="17"/>
       <c r="B50" s="17"/>
       <c r="C50" s="17"/>
@@ -3183,8 +3239,9 @@
       <c r="AD50" s="17"/>
       <c r="AE50" s="17"/>
       <c r="AF50" s="18"/>
-    </row>
-    <row r="51" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AG50" s="17"/>
+    </row>
+    <row r="51" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A51" s="17"/>
       <c r="B51" s="17"/>
       <c r="C51" s="17"/>
@@ -3217,8 +3274,9 @@
       <c r="AD51" s="17"/>
       <c r="AE51" s="17"/>
       <c r="AF51" s="18"/>
-    </row>
-    <row r="52" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AG51" s="17"/>
+    </row>
+    <row r="52" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A52" s="17"/>
       <c r="B52" s="17"/>
       <c r="C52" s="17"/>
@@ -3251,8 +3309,9 @@
       <c r="AD52" s="17"/>
       <c r="AE52" s="17"/>
       <c r="AF52" s="18"/>
-    </row>
-    <row r="53" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AG52" s="17"/>
+    </row>
+    <row r="53" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A53" s="17"/>
       <c r="B53" s="17"/>
       <c r="C53" s="17"/>
@@ -3285,8 +3344,9 @@
       <c r="AD53" s="17"/>
       <c r="AE53" s="17"/>
       <c r="AF53" s="18"/>
-    </row>
-    <row r="54" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AG53" s="17"/>
+    </row>
+    <row r="54" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A54" s="17"/>
       <c r="B54" s="17"/>
       <c r="C54" s="17"/>
@@ -3319,8 +3379,9 @@
       <c r="AD54" s="17"/>
       <c r="AE54" s="17"/>
       <c r="AF54" s="18"/>
-    </row>
-    <row r="55" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AG54" s="17"/>
+    </row>
+    <row r="55" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A55" s="17"/>
       <c r="B55" s="17"/>
       <c r="C55" s="17"/>
@@ -3353,8 +3414,9 @@
       <c r="AD55" s="17"/>
       <c r="AE55" s="17"/>
       <c r="AF55" s="18"/>
-    </row>
-    <row r="56" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AG55" s="17"/>
+    </row>
+    <row r="56" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A56" s="17"/>
       <c r="B56" s="17"/>
       <c r="C56" s="17"/>
@@ -3387,8 +3449,9 @@
       <c r="AD56" s="17"/>
       <c r="AE56" s="17"/>
       <c r="AF56" s="18"/>
-    </row>
-    <row r="57" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AG56" s="17"/>
+    </row>
+    <row r="57" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A57" s="17"/>
       <c r="B57" s="17"/>
       <c r="C57" s="17"/>
@@ -3421,8 +3484,9 @@
       <c r="AD57" s="17"/>
       <c r="AE57" s="17"/>
       <c r="AF57" s="18"/>
-    </row>
-    <row r="58" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AG57" s="17"/>
+    </row>
+    <row r="58" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A58" s="17"/>
       <c r="B58" s="17"/>
       <c r="C58" s="17"/>
@@ -3455,8 +3519,9 @@
       <c r="AD58" s="17"/>
       <c r="AE58" s="17"/>
       <c r="AF58" s="18"/>
-    </row>
-    <row r="59" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AG58" s="17"/>
+    </row>
+    <row r="59" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A59" s="17"/>
       <c r="B59" s="17"/>
       <c r="C59" s="17"/>
@@ -3489,8 +3554,9 @@
       <c r="AD59" s="17"/>
       <c r="AE59" s="17"/>
       <c r="AF59" s="18"/>
-    </row>
-    <row r="60" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AG59" s="17"/>
+    </row>
+    <row r="60" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A60" s="17"/>
       <c r="B60" s="17"/>
       <c r="C60" s="17"/>
@@ -3523,8 +3589,9 @@
       <c r="AD60" s="17"/>
       <c r="AE60" s="17"/>
       <c r="AF60" s="18"/>
-    </row>
-    <row r="61" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AG60" s="17"/>
+    </row>
+    <row r="61" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A61" s="17"/>
       <c r="B61" s="17"/>
       <c r="C61" s="17"/>
@@ -3557,8 +3624,9 @@
       <c r="AD61" s="17"/>
       <c r="AE61" s="17"/>
       <c r="AF61" s="18"/>
-    </row>
-    <row r="62" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AG61" s="17"/>
+    </row>
+    <row r="62" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A62" s="17"/>
       <c r="B62" s="17"/>
       <c r="C62" s="17"/>
@@ -3591,8 +3659,9 @@
       <c r="AD62" s="17"/>
       <c r="AE62" s="17"/>
       <c r="AF62" s="18"/>
-    </row>
-    <row r="63" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AG62" s="17"/>
+    </row>
+    <row r="63" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A63" s="17"/>
       <c r="B63" s="17"/>
       <c r="C63" s="17"/>
@@ -3625,8 +3694,9 @@
       <c r="AD63" s="17"/>
       <c r="AE63" s="17"/>
       <c r="AF63" s="18"/>
-    </row>
-    <row r="64" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AG63" s="17"/>
+    </row>
+    <row r="64" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A64" s="17"/>
       <c r="B64" s="17"/>
       <c r="C64" s="17"/>
@@ -3659,8 +3729,9 @@
       <c r="AD64" s="17"/>
       <c r="AE64" s="17"/>
       <c r="AF64" s="18"/>
-    </row>
-    <row r="65" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AG64" s="17"/>
+    </row>
+    <row r="65" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A65" s="17"/>
       <c r="B65" s="17"/>
       <c r="C65" s="17"/>
@@ -3693,8 +3764,9 @@
       <c r="AD65" s="17"/>
       <c r="AE65" s="17"/>
       <c r="AF65" s="18"/>
-    </row>
-    <row r="66" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AG65" s="17"/>
+    </row>
+    <row r="66" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A66" s="17"/>
       <c r="B66" s="17"/>
       <c r="C66" s="17"/>
@@ -3727,8 +3799,9 @@
       <c r="AD66" s="17"/>
       <c r="AE66" s="17"/>
       <c r="AF66" s="18"/>
-    </row>
-    <row r="67" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AG66" s="17"/>
+    </row>
+    <row r="67" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A67" s="17"/>
       <c r="B67" s="17"/>
       <c r="C67" s="17"/>
@@ -3761,8 +3834,9 @@
       <c r="AD67" s="17"/>
       <c r="AE67" s="17"/>
       <c r="AF67" s="18"/>
-    </row>
-    <row r="68" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AG67" s="17"/>
+    </row>
+    <row r="68" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A68" s="17"/>
       <c r="B68" s="17"/>
       <c r="C68" s="17"/>
@@ -3795,8 +3869,9 @@
       <c r="AD68" s="17"/>
       <c r="AE68" s="17"/>
       <c r="AF68" s="18"/>
-    </row>
-    <row r="69" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AG68" s="17"/>
+    </row>
+    <row r="69" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A69" s="17"/>
       <c r="B69" s="17"/>
       <c r="C69" s="17"/>
@@ -3829,8 +3904,9 @@
       <c r="AD69" s="17"/>
       <c r="AE69" s="17"/>
       <c r="AF69" s="18"/>
-    </row>
-    <row r="70" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AG69" s="17"/>
+    </row>
+    <row r="70" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A70" s="17"/>
       <c r="B70" s="17"/>
       <c r="C70" s="17"/>
@@ -3863,8 +3939,9 @@
       <c r="AD70" s="17"/>
       <c r="AE70" s="17"/>
       <c r="AF70" s="18"/>
-    </row>
-    <row r="71" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AG70" s="17"/>
+    </row>
+    <row r="71" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A71" s="17"/>
       <c r="B71" s="17"/>
       <c r="C71" s="17"/>
@@ -3897,8 +3974,9 @@
       <c r="AD71" s="17"/>
       <c r="AE71" s="17"/>
       <c r="AF71" s="18"/>
-    </row>
-    <row r="72" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AG71" s="17"/>
+    </row>
+    <row r="72" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A72" s="17"/>
       <c r="B72" s="17"/>
       <c r="C72" s="17"/>
@@ -3931,8 +4009,9 @@
       <c r="AD72" s="17"/>
       <c r="AE72" s="17"/>
       <c r="AF72" s="18"/>
-    </row>
-    <row r="73" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AG72" s="17"/>
+    </row>
+    <row r="73" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A73" s="17"/>
       <c r="B73" s="17"/>
       <c r="C73" s="17"/>
@@ -3965,8 +4044,9 @@
       <c r="AD73" s="17"/>
       <c r="AE73" s="17"/>
       <c r="AF73" s="18"/>
-    </row>
-    <row r="74" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AG73" s="17"/>
+    </row>
+    <row r="74" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A74" s="17"/>
       <c r="B74" s="17"/>
       <c r="C74" s="17"/>
@@ -3999,8 +4079,9 @@
       <c r="AD74" s="17"/>
       <c r="AE74" s="17"/>
       <c r="AF74" s="18"/>
-    </row>
-    <row r="75" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AG74" s="17"/>
+    </row>
+    <row r="75" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A75" s="17"/>
       <c r="B75" s="17"/>
       <c r="C75" s="17"/>
@@ -4033,8 +4114,9 @@
       <c r="AD75" s="17"/>
       <c r="AE75" s="17"/>
       <c r="AF75" s="18"/>
-    </row>
-    <row r="76" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AG75" s="17"/>
+    </row>
+    <row r="76" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A76" s="17"/>
       <c r="B76" s="17"/>
       <c r="C76" s="17"/>
@@ -4067,8 +4149,9 @@
       <c r="AD76" s="17"/>
       <c r="AE76" s="17"/>
       <c r="AF76" s="18"/>
-    </row>
-    <row r="77" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AG76" s="17"/>
+    </row>
+    <row r="77" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A77" s="17"/>
       <c r="B77" s="17"/>
       <c r="C77" s="17"/>
@@ -4101,6 +4184,7 @@
       <c r="AD77" s="17"/>
       <c r="AE77" s="17"/>
       <c r="AF77" s="18"/>
+      <c r="AG77" s="17"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -4108,7 +4192,7 @@
     <mergeCell ref="A9:Z9"/>
     <mergeCell ref="A10:J10"/>
     <mergeCell ref="K10:Z10"/>
-    <mergeCell ref="AA10:AF10"/>
+    <mergeCell ref="AA10:AG10"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="V13:V77" xr:uid="{7A47D03C-AF0D-4783-9711-7BE1E853739B}">

--- a/wwwroot/template/TmSendMailNew.xlsx
+++ b/wwwroot/template/TmSendMailNew.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\khanhmf\Cost Managerment\wwwroot\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4526F9A9-069C-4A60-BA0A-F46ABB747F1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62471139-84CA-47E6-BE4D-42D64548B617}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{2DA54543-7852-4C3B-B81A-134334FCB771}"/>
+    <workbookView xWindow="5880" yWindow="1725" windowWidth="21600" windowHeight="11295" xr2:uid="{2DA54543-7852-4C3B-B81A-134334FCB771}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1807,7 +1807,7 @@
         <v>32</v>
       </c>
       <c r="AG11" s="11">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="12" spans="1:45" ht="76.5" x14ac:dyDescent="0.25">
